--- a/input/dataset_modelado_semanal.xlsx
+++ b/input/dataset_modelado_semanal.xlsx
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,299 +435,299 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>semana_inicio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>target_compras_importe_semanal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_lag_1s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_lag_2s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_lag_4s</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_lag_8s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_lag_52s</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_media_4s</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_desv_4s</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_media_8s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_desv_8s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_media_12s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hist_compras_importe_semanal_desv_12s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_lag_1s</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_lag_2s</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_lag_4s</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_lag_8s</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_lag_52s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_media_4s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_desv_4s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_media_8s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_desv_8s</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_media_12s</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_importe_real_2026_05_desv_12s</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_lag_1s</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_lag_2s</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_lag_4s</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_lag_8s</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_lag_52s</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_media_4s</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_desv_4s</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_media_8s</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_desv_8s</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_media_12s</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_registros_desv_12s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_lag_1s</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_lag_2s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_lag_4s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_lag_8s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_lag_52s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_media_4s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_desv_4s</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_media_8s</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_desv_8s</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_media_12s</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>hist_ventas_cantidad_total_desv_12s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>exog_eventos_festivos_semana</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>exog_eventos_pago_semana</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>exog_es_san_valentin</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>exog_es_dia_nino</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>exog_es_dia_madre</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>exog_nacimientos_indice_semanal</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>exog_semana_anio_sin</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>exog_semana_anio_cos</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>exog_mes_sin</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>exog_mes_cos</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>exog_inpc_publicado</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>exog_temperatura_lag_1s</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44928</v>
       </c>
       <c r="B2" t="n">
@@ -773,7 +785,7 @@
         <v>1172.679028132993</v>
       </c>
       <c r="T2" t="n">
-        <v>816.2498216428297</v>
+        <v>816.2498216428307</v>
       </c>
       <c r="U2" t="n">
         <v>1213.91932257853</v>
@@ -806,7 +818,7 @@
         <v>3.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.499999999999998</v>
       </c>
       <c r="AF2" t="n">
         <v>3.125</v>
@@ -891,7 +903,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44935</v>
       </c>
       <c r="B3" t="n">
@@ -949,7 +961,7 @@
         <v>1195.765687190614</v>
       </c>
       <c r="T3" t="n">
-        <v>780.1331903248996</v>
+        <v>780.1331903249009</v>
       </c>
       <c r="U3" t="n">
         <v>1048.603185912836</v>
@@ -982,7 +994,7 @@
         <v>3.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>1.499999999999998</v>
       </c>
       <c r="AF3" t="n">
         <v>2.875</v>
@@ -1067,7 +1079,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="B4" t="n">
@@ -1125,7 +1137,7 @@
         <v>830.9254529052869</v>
       </c>
       <c r="T4" t="n">
-        <v>426.5032725207849</v>
+        <v>426.5032725207868</v>
       </c>
       <c r="U4" t="n">
         <v>1138.884475419789</v>
@@ -1158,7 +1170,7 @@
         <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.258305739211791</v>
+        <v>1.25830573921179</v>
       </c>
       <c r="AF4" t="n">
         <v>3</v>
@@ -1243,7 +1255,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44949</v>
       </c>
       <c r="B5" t="n">
@@ -1301,7 +1313,7 @@
         <v>796.1250771951721</v>
       </c>
       <c r="T5" t="n">
-        <v>379.6884803955083</v>
+        <v>379.6884803955103</v>
       </c>
       <c r="U5" t="n">
         <v>1191.788832125031</v>
@@ -1334,7 +1346,7 @@
         <v>2.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.732050807568877</v>
+        <v>1.732050807568876</v>
       </c>
       <c r="AF5" t="n">
         <v>3.25</v>
@@ -1419,7 +1431,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="B6" t="n">
@@ -1477,7 +1489,7 @@
         <v>1144.517699115044</v>
       </c>
       <c r="T6" t="n">
-        <v>914.0964894335543</v>
+        <v>914.0964894335555</v>
       </c>
       <c r="U6" t="n">
         <v>1158.598363624018</v>
@@ -1510,7 +1522,7 @@
         <v>2.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659931</v>
       </c>
       <c r="AF6" t="n">
         <v>3</v>
@@ -1595,7 +1607,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="B7" t="n">
@@ -1653,7 +1665,7 @@
         <v>1122.753445089275</v>
       </c>
       <c r="T7" t="n">
-        <v>941.7199028469025</v>
+        <v>941.7199028469034</v>
       </c>
       <c r="U7" t="n">
         <v>1159.259566139944</v>
@@ -1686,7 +1698,7 @@
         <v>2.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.914854215512676</v>
+        <v>1.914854215512675</v>
       </c>
       <c r="AF7" t="n">
         <v>2.875</v>
@@ -1771,7 +1783,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="B8" t="n">
@@ -1829,7 +1841,7 @@
         <v>1205.891653476944</v>
       </c>
       <c r="T8" t="n">
-        <v>908.6759168828697</v>
+        <v>908.675916882871</v>
       </c>
       <c r="U8" t="n">
         <v>1018.408553191115</v>
@@ -1947,7 +1959,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44977</v>
       </c>
       <c r="B9" t="n">
@@ -2005,7 +2017,7 @@
         <v>1264.667232414532</v>
       </c>
       <c r="T9" t="n">
-        <v>911.5081555313369</v>
+        <v>911.508155531338</v>
       </c>
       <c r="U9" t="n">
         <v>1030.396154804852</v>
@@ -2038,7 +2050,7 @@
         <v>4.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.304037933599835</v>
+        <v>3.304037933599834</v>
       </c>
       <c r="AF9" t="n">
         <v>3.625</v>
@@ -2123,7 +2135,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="B10" t="n">
@@ -2181,7 +2193,7 @@
         <v>661.8372703412074</v>
       </c>
       <c r="T10" t="n">
-        <v>664.2029025703235</v>
+        <v>664.2029025703249</v>
       </c>
       <c r="U10" t="n">
         <v>903.1774847281258</v>
@@ -2299,7 +2311,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44991</v>
       </c>
       <c r="B11" t="n">
@@ -2357,7 +2369,7 @@
         <v>1125.408308906642</v>
       </c>
       <c r="T11" t="n">
-        <v>859.2296029301549</v>
+        <v>859.229602930156</v>
       </c>
       <c r="U11" t="n">
         <v>1124.080876997959</v>
@@ -2475,7 +2487,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44998</v>
       </c>
       <c r="B12" t="n">
@@ -2533,7 +2545,7 @@
         <v>1037.138178439374</v>
       </c>
       <c r="T12" t="n">
-        <v>886.6011008023592</v>
+        <v>886.6011008023604</v>
       </c>
       <c r="U12" t="n">
         <v>1121.514915958159</v>
@@ -2566,7 +2578,7 @@
         <v>3.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269013</v>
       </c>
       <c r="AF12" t="n">
         <v>3.75</v>
@@ -2651,7 +2663,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45005</v>
       </c>
       <c r="B13" t="n">
@@ -2709,7 +2721,7 @@
         <v>1009.934009617411</v>
       </c>
       <c r="T13" t="n">
-        <v>873.9187451253488</v>
+        <v>873.9187451253499</v>
       </c>
       <c r="U13" t="n">
         <v>1137.300621015972</v>
@@ -2742,7 +2754,7 @@
         <v>2.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.06155281280883</v>
+        <v>2.061552812808829</v>
       </c>
       <c r="AF13" t="n">
         <v>3.75</v>
@@ -2827,7 +2839,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="B14" t="n">
@@ -2885,7 +2897,7 @@
         <v>1714.532549763396</v>
       </c>
       <c r="T14" t="n">
-        <v>923.0252654528593</v>
+        <v>923.0252654528605</v>
       </c>
       <c r="U14" t="n">
         <v>1188.184910052302</v>
@@ -2918,7 +2930,7 @@
         <v>3.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.9574271077563378</v>
+        <v>0.9574271077563352</v>
       </c>
       <c r="AF14" t="n">
         <v>3.875</v>
@@ -3003,7 +3015,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45019</v>
       </c>
       <c r="B15" t="n">
@@ -3061,7 +3073,7 @@
         <v>1232.328467153284</v>
       </c>
       <c r="T15" t="n">
-        <v>1156.02974457765</v>
+        <v>1156.029744577651</v>
       </c>
       <c r="U15" t="n">
         <v>1178.868388029963</v>
@@ -3094,7 +3106,7 @@
         <v>3.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659931</v>
       </c>
       <c r="AF15" t="n">
         <v>3.875</v>
@@ -3179,7 +3191,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="B16" t="n">
@@ -3237,7 +3249,7 @@
         <v>1463.505810218978</v>
       </c>
       <c r="T16" t="n">
-        <v>1105.926081471541</v>
+        <v>1105.926081471542</v>
       </c>
       <c r="U16" t="n">
         <v>1250.321994329176</v>
@@ -3270,7 +3282,7 @@
         <v>3.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659931</v>
       </c>
       <c r="AF16" t="n">
         <v>3.25</v>
@@ -3355,7 +3367,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45033</v>
       </c>
       <c r="B17" t="n">
@@ -3413,7 +3425,7 @@
         <v>1183.679532846715</v>
       </c>
       <c r="T17" t="n">
-        <v>1294.420935483727</v>
+        <v>1294.420935483728</v>
       </c>
       <c r="U17" t="n">
         <v>1096.806771232063</v>
@@ -3446,7 +3458,7 @@
         <v>2.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.499999999999998</v>
       </c>
       <c r="AF17" t="n">
         <v>2.5</v>
@@ -3531,7 +3543,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="B18" t="n">
@@ -3589,7 +3601,7 @@
         <v>594.1289927007297</v>
       </c>
       <c r="T18" t="n">
-        <v>704.1400460032983</v>
+        <v>704.1400460032997</v>
       </c>
       <c r="U18" t="n">
         <v>1154.330771232063</v>
@@ -3622,7 +3634,7 @@
         <v>1.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.9574271077563375</v>
+        <v>0.9574271077563351</v>
       </c>
       <c r="AF18" t="n">
         <v>2.75</v>
@@ -3707,7 +3719,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B19" t="n">
@@ -3765,7 +3777,7 @@
         <v>1208.792</v>
       </c>
       <c r="T19" t="n">
-        <v>1118.059912164519</v>
+        <v>1118.05991216452</v>
       </c>
       <c r="U19" t="n">
         <v>1220.560233576642</v>
@@ -3798,7 +3810,7 @@
         <v>2.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.9574271077563375</v>
+        <v>0.9574271077563351</v>
       </c>
       <c r="AF19" t="n">
         <v>2.75</v>
@@ -3883,7 +3895,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="B20" t="n">
@@ -3941,7 +3953,7 @@
         <v>1054.337253424657</v>
       </c>
       <c r="T20" t="n">
-        <v>1083.266246676539</v>
+        <v>1083.26624667654</v>
       </c>
       <c r="U20" t="n">
         <v>1258.921531821818</v>
@@ -3974,7 +3986,7 @@
         <v>2.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.290994448735805</v>
+        <v>1.290994448735803</v>
       </c>
       <c r="AF20" t="n">
         <v>2.875</v>
@@ -4059,7 +4071,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45061</v>
       </c>
       <c r="B21" t="n">
@@ -4117,7 +4129,7 @@
         <v>1136.375609589041</v>
       </c>
       <c r="T21" t="n">
-        <v>1002.102121325183</v>
+        <v>1002.102121325184</v>
       </c>
       <c r="U21" t="n">
         <v>1160.027571217878</v>
@@ -4150,7 +4162,7 @@
         <v>2.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.290994448735805</v>
+        <v>1.290994448735803</v>
       </c>
       <c r="AF21" t="n">
         <v>2.375</v>
@@ -4235,7 +4247,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45068</v>
       </c>
       <c r="B22" t="n">
@@ -4293,7 +4305,7 @@
         <v>1188.305349315068</v>
       </c>
       <c r="T22" t="n">
-        <v>959.8739584420676</v>
+        <v>959.8739584420688</v>
       </c>
       <c r="U22" t="n">
         <v>891.2171710078992</v>
@@ -4326,7 +4338,7 @@
         <v>2.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.258305739211791</v>
+        <v>1.258305739211789</v>
       </c>
       <c r="AF22" t="n">
         <v>2.25</v>
@@ -4411,7 +4423,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45075</v>
       </c>
       <c r="B23" t="n">
@@ -4502,7 +4514,7 @@
         <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.414213562373095</v>
+        <v>1.414213562373093</v>
       </c>
       <c r="AF23" t="n">
         <v>2.625</v>
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45082</v>
       </c>
       <c r="B24" t="n">
@@ -4645,7 +4657,7 @@
         <v>1310.522260273973</v>
       </c>
       <c r="T24" t="n">
-        <v>1525.933315773127</v>
+        <v>1525.933315773128</v>
       </c>
       <c r="U24" t="n">
         <v>1182.429756849315</v>
@@ -4678,7 +4690,7 @@
         <v>2.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.5</v>
+        <v>1.499999999999998</v>
       </c>
       <c r="AF24" t="n">
         <v>2.375</v>
@@ -4763,7 +4775,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="B25" t="n">
@@ -4821,7 +4833,7 @@
         <v>1274.736078022632</v>
       </c>
       <c r="T25" t="n">
-        <v>1553.158919275314</v>
+        <v>1553.158919275315</v>
       </c>
       <c r="U25" t="n">
         <v>1205.555843805837</v>
@@ -4854,7 +4866,7 @@
         <v>2.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.5</v>
+        <v>1.499999999999998</v>
       </c>
       <c r="AF25" t="n">
         <v>2.375</v>
@@ -4939,7 +4951,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="B26" t="n">
@@ -5030,7 +5042,7 @@
         <v>2.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.499999999999998</v>
       </c>
       <c r="AF26" t="n">
         <v>2.5</v>
@@ -5115,7 +5127,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B27" t="n">
@@ -5173,7 +5185,7 @@
         <v>387.8680830039523</v>
       </c>
       <c r="T27" t="n">
-        <v>162.1788172295396</v>
+        <v>162.1788172295453</v>
       </c>
       <c r="U27" t="n">
         <v>913.7092983512915</v>
@@ -5206,7 +5218,7 @@
         <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.9999999999999991</v>
+        <v>0.9999999999999967</v>
       </c>
       <c r="AF27" t="n">
         <v>2.25</v>
@@ -5291,7 +5303,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B28" t="n">
@@ -5349,7 +5361,7 @@
         <v>725.3693878056226</v>
       </c>
       <c r="T28" t="n">
-        <v>759.0122404081958</v>
+        <v>759.012240408197</v>
       </c>
       <c r="U28" t="n">
         <v>1017.945824039798</v>
@@ -5382,7 +5394,7 @@
         <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.154700538379251</v>
+        <v>1.154700538379249</v>
       </c>
       <c r="AF28" t="n">
         <v>2.125</v>
@@ -5467,7 +5479,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B29" t="n">
@@ -5525,7 +5537,7 @@
         <v>1001.637881951034</v>
       </c>
       <c r="T29" t="n">
-        <v>774.2162387952042</v>
+        <v>774.2162387952054</v>
       </c>
       <c r="U29" t="n">
         <v>1138.186979986834</v>
@@ -5558,7 +5570,7 @@
         <v>2.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.9574271077563372</v>
+        <v>0.9574271077563348</v>
       </c>
       <c r="AF29" t="n">
         <v>2.25</v>
@@ -5643,7 +5655,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="B30" t="n">
@@ -5701,7 +5713,7 @@
         <v>1058.561871322832</v>
       </c>
       <c r="T30" t="n">
-        <v>736.1268692732833</v>
+        <v>736.1268692732846</v>
       </c>
       <c r="U30" t="n">
         <v>1150.319195718809</v>
@@ -5734,7 +5746,7 @@
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.8164965809277249</v>
+        <v>0.816496580927722</v>
       </c>
       <c r="AF30" t="n">
         <v>2.125</v>
@@ -5819,7 +5831,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="B31" t="n">
@@ -5877,7 +5889,7 @@
         <v>1235.876826722338</v>
       </c>
       <c r="T31" t="n">
-        <v>501.7929813351615</v>
+        <v>501.7929813351634</v>
       </c>
       <c r="U31" t="n">
         <v>811.8724548631455</v>
@@ -5910,7 +5922,7 @@
         <v>2.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.5773502691896242</v>
+        <v>0.5773502691896201</v>
       </c>
       <c r="AF31" t="n">
         <v>2</v>
@@ -5995,7 +6007,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B32" t="n">
@@ -6053,7 +6065,7 @@
         <v>1498.063674321503</v>
       </c>
       <c r="T32" t="n">
-        <v>975.139612588285</v>
+        <v>975.1396125882859</v>
       </c>
       <c r="U32" t="n">
         <v>1111.716531063563</v>
@@ -6086,7 +6098,7 @@
         <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.414213562373094</v>
+        <v>1.414213562373093</v>
       </c>
       <c r="AF32" t="n">
         <v>2.5</v>
@@ -6171,7 +6183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="B33" t="n">
@@ -6262,7 +6274,7 @@
         <v>5</v>
       </c>
       <c r="AE33" t="n">
-        <v>3.559026084010437</v>
+        <v>3.559026084010436</v>
       </c>
       <c r="AF33" t="n">
         <v>3.625</v>
@@ -6347,7 +6359,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45152</v>
       </c>
       <c r="B34" t="n">
@@ -6438,7 +6450,7 @@
         <v>5.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>3.109126351029604</v>
+        <v>3.109126351029603</v>
       </c>
       <c r="AF34" t="n">
         <v>3.75</v>
@@ -6523,7 +6535,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45159</v>
       </c>
       <c r="B35" t="n">
@@ -6581,7 +6593,7 @@
         <v>3070.316121949463</v>
       </c>
       <c r="T35" t="n">
-        <v>1993.782159421064</v>
+        <v>1993.782159421065</v>
       </c>
       <c r="U35" t="n">
         <v>2153.096474335901</v>
@@ -6614,7 +6626,7 @@
         <v>6.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.64575131106459</v>
+        <v>2.645751311064589</v>
       </c>
       <c r="AF35" t="n">
         <v>4.5</v>
@@ -6699,7 +6711,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="B36" t="n">
@@ -6757,7 +6769,7 @@
         <v>2752.966331617594</v>
       </c>
       <c r="T36" t="n">
-        <v>2128.27306483875</v>
+        <v>2128.273064838751</v>
       </c>
       <c r="U36" t="n">
         <v>2125.515002969549</v>
@@ -6790,7 +6802,7 @@
         <v>6</v>
       </c>
       <c r="AE36" t="n">
-        <v>3.162277660168379</v>
+        <v>3.162277660168378</v>
       </c>
       <c r="AF36" t="n">
         <v>4.5</v>
@@ -6875,7 +6887,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45173</v>
       </c>
       <c r="B37" t="n">
@@ -6966,7 +6978,7 @@
         <v>5.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.061552812808829</v>
+        <v>2.061552812808828</v>
       </c>
       <c r="AF37" t="n">
         <v>5.125</v>
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="B38" t="n">
@@ -7109,7 +7121,7 @@
         <v>3205.758063734987</v>
       </c>
       <c r="T38" t="n">
-        <v>2254.491953963282</v>
+        <v>2254.491953963283</v>
       </c>
       <c r="U38" t="n">
         <v>3021.936537626618</v>
@@ -7142,7 +7154,7 @@
         <v>5.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.061552812808829</v>
+        <v>2.061552812808828</v>
       </c>
       <c r="AF38" t="n">
         <v>5.375</v>
@@ -7227,7 +7239,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45187</v>
       </c>
       <c r="B39" t="n">
@@ -7318,7 +7330,7 @@
         <v>4</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.160246899469286</v>
+        <v>2.160246899469285</v>
       </c>
       <c r="AF39" t="n">
         <v>5.25</v>
@@ -7403,7 +7415,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45194</v>
       </c>
       <c r="B40" t="n">
@@ -7494,7 +7506,7 @@
         <v>4.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.061552812808829</v>
+        <v>2.061552812808828</v>
       </c>
       <c r="AF40" t="n">
         <v>5.125</v>
@@ -7579,7 +7591,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45201</v>
       </c>
       <c r="B41" t="n">
@@ -7670,7 +7682,7 @@
         <v>3</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.15470053837925</v>
+        <v>1.154700538379248</v>
       </c>
       <c r="AF41" t="n">
         <v>4.125</v>
@@ -7755,7 +7767,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45208</v>
       </c>
       <c r="B42" t="n">
@@ -7813,7 +7825,7 @@
         <v>1467.201587803977</v>
       </c>
       <c r="T42" t="n">
-        <v>1336.317506127713</v>
+        <v>1336.317506127714</v>
       </c>
       <c r="U42" t="n">
         <v>2336.479825769482</v>
@@ -7846,7 +7858,7 @@
         <v>3</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.15470053837925</v>
+        <v>1.154700538379248</v>
       </c>
       <c r="AF42" t="n">
         <v>4.125</v>
@@ -7931,7 +7943,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45215</v>
       </c>
       <c r="B43" t="n">
@@ -7989,7 +8001,7 @@
         <v>2090.385424909004</v>
       </c>
       <c r="T43" t="n">
-        <v>1330.057682049064</v>
+        <v>1330.057682049065</v>
       </c>
       <c r="U43" t="n">
         <v>2486.22510057926</v>
@@ -8022,7 +8034,7 @@
         <v>4</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.632993161855451</v>
+        <v>1.632993161855449</v>
       </c>
       <c r="AF43" t="n">
         <v>4</v>
@@ -8107,7 +8119,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="B44" t="n">
@@ -8165,7 +8177,7 @@
         <v>1630.549889222978</v>
       </c>
       <c r="T44" t="n">
-        <v>1097.495917992607</v>
+        <v>1097.495917992608</v>
       </c>
       <c r="U44" t="n">
         <v>2458.643067432102</v>
@@ -8198,7 +8210,7 @@
         <v>4.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.707825127659932</v>
+        <v>1.707825127659931</v>
       </c>
       <c r="AF44" t="n">
         <v>4.25</v>
@@ -8283,7 +8295,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="B45" t="n">
@@ -8341,7 +8353,7 @@
         <v>1655.308685446009</v>
       </c>
       <c r="T45" t="n">
-        <v>1059.56473680574</v>
+        <v>1059.564736805741</v>
       </c>
       <c r="U45" t="n">
         <v>1705.300410138735</v>
@@ -8374,7 +8386,7 @@
         <v>4.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.707825127659932</v>
+        <v>1.707825127659931</v>
       </c>
       <c r="AF45" t="n">
         <v>3.625</v>
@@ -8459,7 +8471,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45236</v>
       </c>
       <c r="B46" t="n">
@@ -8550,7 +8562,7 @@
         <v>4.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.732050807568876</v>
+        <v>1.732050807568875</v>
       </c>
       <c r="AF46" t="n">
         <v>3.75</v>
@@ -8635,7 +8647,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="B47" t="n">
@@ -8811,7 +8823,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45250</v>
       </c>
       <c r="B48" t="n">
@@ -8869,7 +8881,7 @@
         <v>2801.20614893062</v>
       </c>
       <c r="T48" t="n">
-        <v>3172.787463238193</v>
+        <v>3172.787463238194</v>
       </c>
       <c r="U48" t="n">
         <v>2215.878019076799</v>
@@ -8902,7 +8914,7 @@
         <v>3.75</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.753785273643051</v>
+        <v>2.75378527364305</v>
       </c>
       <c r="AF48" t="n">
         <v>4</v>
@@ -8987,7 +8999,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45257</v>
       </c>
       <c r="B49" t="n">
@@ -9078,7 +9090,7 @@
         <v>4</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.581988897471611</v>
+        <v>2.58198889747161</v>
       </c>
       <c r="AF49" t="n">
         <v>4.125</v>
@@ -9163,7 +9175,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45264</v>
       </c>
       <c r="B50" t="n">
@@ -9221,7 +9233,7 @@
         <v>2522.095553171196</v>
       </c>
       <c r="T50" t="n">
-        <v>1749.655693318123</v>
+        <v>1749.655693318124</v>
       </c>
       <c r="U50" t="n">
         <v>2747.41123511455</v>
@@ -9254,7 +9266,7 @@
         <v>4.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.753785273643051</v>
+        <v>2.75378527364305</v>
       </c>
       <c r="AF50" t="n">
         <v>4.375</v>
@@ -9339,7 +9351,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45271</v>
       </c>
       <c r="B51" t="n">
@@ -9397,7 +9409,7 @@
         <v>3672.426730646955</v>
       </c>
       <c r="T51" t="n">
-        <v>1195.419219728688</v>
+        <v>1195.419219728689</v>
       </c>
       <c r="U51" t="n">
         <v>2978.748495083519</v>
@@ -9515,7 +9527,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="B52" t="n">
@@ -9573,7 +9585,7 @@
         <v>3315.401416706406</v>
       </c>
       <c r="T52" t="n">
-        <v>1461.394684732071</v>
+        <v>1461.394684732072</v>
       </c>
       <c r="U52" t="n">
         <v>3058.303782818513</v>
@@ -9691,7 +9703,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45285</v>
       </c>
       <c r="B53" t="n">
@@ -9749,7 +9761,7 @@
         <v>2466.199034334763</v>
       </c>
       <c r="T53" t="n">
-        <v>1697.926519775425</v>
+        <v>1697.926519775426</v>
       </c>
       <c r="U53" t="n">
         <v>3109.455150970199</v>
@@ -9782,7 +9794,7 @@
         <v>6.75</v>
       </c>
       <c r="AE53" t="n">
-        <v>4.112987559751022</v>
+        <v>4.112987559751021</v>
       </c>
       <c r="AF53" t="n">
         <v>5.375</v>
@@ -9867,7 +9879,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B54" t="n">
@@ -9958,7 +9970,7 @@
         <v>7.25</v>
       </c>
       <c r="AE54" t="n">
-        <v>4.112987559751022</v>
+        <v>4.112987559751021</v>
       </c>
       <c r="AF54" t="n">
         <v>5.75</v>
@@ -10043,7 +10055,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45299</v>
       </c>
       <c r="B55" t="n">
@@ -10101,7 +10113,7 @@
         <v>1795.396050270878</v>
       </c>
       <c r="T55" t="n">
-        <v>624.2825992254886</v>
+        <v>624.2825992254907</v>
       </c>
       <c r="U55" t="n">
         <v>2733.911390458917</v>
@@ -10134,7 +10146,7 @@
         <v>5.25</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.753785273643051</v>
+        <v>2.75378527364305</v>
       </c>
       <c r="AF55" t="n">
         <v>6.125</v>
@@ -10219,7 +10231,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B56" t="n">
@@ -10277,7 +10289,7 @@
         <v>1788.578392140997</v>
       </c>
       <c r="T56" t="n">
-        <v>620.8949973651871</v>
+        <v>620.8949973651892</v>
       </c>
       <c r="U56" t="n">
         <v>2551.989904423701</v>
@@ -10310,7 +10322,7 @@
         <v>4.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.516611478423583</v>
+        <v>2.516611478423582</v>
       </c>
       <c r="AF56" t="n">
         <v>5.75</v>
@@ -10395,7 +10407,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="B57" t="n">
@@ -10453,7 +10465,7 @@
         <v>1678.945771476816</v>
       </c>
       <c r="T57" t="n">
-        <v>839.2606735929779</v>
+        <v>839.2606735929794</v>
       </c>
       <c r="U57" t="n">
         <v>2072.57240290579</v>
@@ -10486,7 +10498,7 @@
         <v>4.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.516611478423583</v>
+        <v>2.516611478423582</v>
       </c>
       <c r="AF57" t="n">
         <v>5.625</v>
@@ -10571,7 +10583,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="B58" t="n">
@@ -10629,7 +10641,7 @@
         <v>1402.817622950819</v>
       </c>
       <c r="T58" t="n">
-        <v>830.1763964871977</v>
+        <v>830.1763964871992</v>
       </c>
       <c r="U58" t="n">
         <v>1936.357845810174</v>
@@ -10662,7 +10674,7 @@
         <v>3.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999972</v>
       </c>
       <c r="AF58" t="n">
         <v>5.375</v>
@@ -10747,7 +10759,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="B59" t="n">
@@ -10923,7 +10935,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B60" t="n">
@@ -10981,7 +10993,7 @@
         <v>2760.679023845007</v>
       </c>
       <c r="T60" t="n">
-        <v>3194.42161079525</v>
+        <v>3194.421610795251</v>
       </c>
       <c r="U60" t="n">
         <v>2274.628707993003</v>
@@ -11099,7 +11111,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45341</v>
       </c>
       <c r="B61" t="n">
@@ -11275,7 +11287,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="B62" t="n">
@@ -11366,7 +11378,7 @@
         <v>8</v>
       </c>
       <c r="AE62" t="n">
-        <v>4.242640687119285</v>
+        <v>4.242640687119284</v>
       </c>
       <c r="AF62" t="n">
         <v>5.75</v>
@@ -11451,7 +11463,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45355</v>
       </c>
       <c r="B63" t="n">
@@ -11542,7 +11554,7 @@
         <v>7</v>
       </c>
       <c r="AE63" t="n">
-        <v>3.741657386773941</v>
+        <v>3.74165738677394</v>
       </c>
       <c r="AF63" t="n">
         <v>6.125</v>
@@ -11627,7 +11639,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45362</v>
       </c>
       <c r="B64" t="n">
@@ -11685,7 +11697,7 @@
         <v>3646.627211024269</v>
       </c>
       <c r="T64" t="n">
-        <v>3102.566413974536</v>
+        <v>3102.566413974537</v>
       </c>
       <c r="U64" t="n">
         <v>3203.653117434639</v>
@@ -11803,7 +11815,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="B65" t="n">
@@ -11894,7 +11906,7 @@
         <v>4</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.160246899469286</v>
+        <v>2.160246899469285</v>
       </c>
       <c r="AF65" t="n">
         <v>6.125</v>
@@ -11979,7 +11991,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="B66" t="n">
@@ -12155,7 +12167,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B67" t="n">
@@ -12213,7 +12225,7 @@
         <v>1789.490950226244</v>
       </c>
       <c r="T67" t="n">
-        <v>1400.767350027055</v>
+        <v>1400.767350027056</v>
       </c>
       <c r="U67" t="n">
         <v>2749.379730563554</v>
@@ -12331,7 +12343,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B68" t="n">
@@ -12389,7 +12401,7 @@
         <v>1505.023256945458</v>
       </c>
       <c r="T68" t="n">
-        <v>1475.111529412843</v>
+        <v>1475.111529412844</v>
       </c>
       <c r="U68" t="n">
         <v>2575.825233984864</v>
@@ -12422,7 +12434,7 @@
         <v>3.5</v>
       </c>
       <c r="AE68" t="n">
-        <v>3</v>
+        <v>2.999999999999999</v>
       </c>
       <c r="AF68" t="n">
         <v>5</v>
@@ -12507,7 +12519,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B69" t="n">
@@ -12598,7 +12610,7 @@
         <v>4.25</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269013</v>
       </c>
       <c r="AF69" t="n">
         <v>4.125</v>
@@ -12683,7 +12695,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45404</v>
       </c>
       <c r="B70" t="n">
@@ -12741,7 +12753,7 @@
         <v>2795.49163139201</v>
       </c>
       <c r="T70" t="n">
-        <v>1779.761438872099</v>
+        <v>1779.7614388721</v>
       </c>
       <c r="U70" t="n">
         <v>2841.873926555734</v>
@@ -12774,7 +12786,7 @@
         <v>4.25</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269013</v>
       </c>
       <c r="AF70" t="n">
         <v>4</v>
@@ -12859,7 +12871,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="B71" t="n">
@@ -12917,7 +12929,7 @@
         <v>2003.892473118279</v>
       </c>
       <c r="T71" t="n">
-        <v>1930.935477454058</v>
+        <v>1930.935477454059</v>
       </c>
       <c r="U71" t="n">
         <v>1896.691711672262</v>
@@ -12950,7 +12962,7 @@
         <v>2.5</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.732050807568876</v>
+        <v>1.732050807568875</v>
       </c>
       <c r="AF71" t="n">
         <v>3.25</v>
@@ -13035,7 +13047,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="B72" t="n">
@@ -13093,7 +13105,7 @@
         <v>4769.455499002682</v>
       </c>
       <c r="T72" t="n">
-        <v>5041.562160683459</v>
+        <v>5041.56216068346</v>
       </c>
       <c r="U72" t="n">
         <v>3137.23937797407</v>
@@ -13126,7 +13138,7 @@
         <v>4.5</v>
       </c>
       <c r="AE72" t="n">
-        <v>4.041451884327381</v>
+        <v>4.04145188432738</v>
       </c>
       <c r="AF72" t="n">
         <v>4</v>
@@ -13211,7 +13223,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45425</v>
       </c>
       <c r="B73" t="n">
@@ -13302,7 +13314,7 @@
         <v>5</v>
       </c>
       <c r="AE73" t="n">
-        <v>4.242640687119285</v>
+        <v>4.242640687119284</v>
       </c>
       <c r="AF73" t="n">
         <v>4.625</v>
@@ -13387,7 +13399,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45432</v>
       </c>
       <c r="B74" t="n">
@@ -13563,7 +13575,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45439</v>
       </c>
       <c r="B75" t="n">
@@ -13739,7 +13751,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B76" t="n">
@@ -13830,7 +13842,7 @@
         <v>4</v>
       </c>
       <c r="AE76" t="n">
-        <v>3.559026084010437</v>
+        <v>3.559026084010436</v>
       </c>
       <c r="AF76" t="n">
         <v>4.25</v>
@@ -13915,7 +13927,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="B77" t="n">
@@ -13940,7 +13952,7 @@
         <v>105.2011646586344</v>
       </c>
       <c r="I77" t="n">
-        <v>210.4023293172691</v>
+        <v>210.4023293172711</v>
       </c>
       <c r="J77" t="n">
         <v>220.8391785188765</v>
@@ -14006,7 +14018,7 @@
         <v>3.25</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.986078811194819</v>
+        <v>2.986078811194818</v>
       </c>
       <c r="AF77" t="n">
         <v>4.125</v>
@@ -14091,7 +14103,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B78" t="n">
@@ -14116,7 +14128,7 @@
         <v>105.2011646586344</v>
       </c>
       <c r="I78" t="n">
-        <v>210.4023293172691</v>
+        <v>210.4023293172711</v>
       </c>
       <c r="J78" t="n">
         <v>220.8391785188765</v>
@@ -14182,7 +14194,7 @@
         <v>3.5</v>
       </c>
       <c r="AE78" t="n">
-        <v>3.415650255319866</v>
+        <v>3.415650255319865</v>
       </c>
       <c r="AF78" t="n">
         <v>4.875</v>
@@ -14267,7 +14279,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B79" t="n">
@@ -14292,7 +14304,7 @@
         <v>105.2011646586344</v>
       </c>
       <c r="I79" t="n">
-        <v>210.4023293172691</v>
+        <v>210.4023293172711</v>
       </c>
       <c r="J79" t="n">
         <v>207.17627529307</v>
@@ -14358,7 +14370,7 @@
         <v>4.5</v>
       </c>
       <c r="AE79" t="n">
-        <v>3.415650255319866</v>
+        <v>3.415650255319865</v>
       </c>
       <c r="AF79" t="n">
         <v>5.5</v>
@@ -14443,7 +14455,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B80" t="n">
@@ -14468,7 +14480,7 @@
         <v>105.2011646586344</v>
       </c>
       <c r="I80" t="n">
-        <v>210.4023293172691</v>
+        <v>210.4023293172711</v>
       </c>
       <c r="J80" t="n">
         <v>52.60058232931738</v>
@@ -14534,7 +14546,7 @@
         <v>5.75</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.707825127659932</v>
+        <v>1.70782512765993</v>
       </c>
       <c r="AF80" t="n">
         <v>4.875</v>
@@ -14619,7 +14631,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B81" t="n">
@@ -14710,7 +14722,7 @@
         <v>6.25</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.25830573921179</v>
+        <v>1.258305739211788</v>
       </c>
       <c r="AF81" t="n">
         <v>4.75</v>
@@ -14795,7 +14807,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B82" t="n">
@@ -14886,7 +14898,7 @@
         <v>6</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.8164965809277231</v>
+        <v>0.8164965809277203</v>
       </c>
       <c r="AF82" t="n">
         <v>4.75</v>
@@ -14971,7 +14983,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="B83" t="n">
@@ -15062,7 +15074,7 @@
         <v>5</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.160246899469286</v>
+        <v>2.160246899469285</v>
       </c>
       <c r="AF83" t="n">
         <v>4.75</v>
@@ -15147,7 +15159,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B84" t="n">
@@ -15238,7 +15250,7 @@
         <v>4</v>
       </c>
       <c r="AE84" t="n">
-        <v>2.943920288775948</v>
+        <v>2.943920288775947</v>
       </c>
       <c r="AF84" t="n">
         <v>4.875</v>
@@ -15323,7 +15335,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="B85" t="n">
@@ -15414,7 +15426,7 @@
         <v>3</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.708012801545319</v>
+        <v>2.708012801545318</v>
       </c>
       <c r="AF85" t="n">
         <v>4.625</v>
@@ -15499,7 +15511,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="B86" t="n">
@@ -15590,7 +15602,7 @@
         <v>1.5</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.577350269189622</v>
+        <v>0.577350269189618</v>
       </c>
       <c r="AF86" t="n">
         <v>3.75</v>
@@ -15675,7 +15687,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B87" t="n">
@@ -15766,7 +15778,7 @@
         <v>1.75</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.9574271077563359</v>
+        <v>0.9574271077563334</v>
       </c>
       <c r="AF87" t="n">
         <v>3.375</v>
@@ -15851,7 +15863,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45530</v>
       </c>
       <c r="B88" t="n">
@@ -15942,7 +15954,7 @@
         <v>2.25</v>
       </c>
       <c r="AE88" t="n">
-        <v>0.9574271077563359</v>
+        <v>0.9574271077563334</v>
       </c>
       <c r="AF88" t="n">
         <v>3.125</v>
@@ -16027,7 +16039,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B89" t="n">
@@ -16203,7 +16215,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B90" t="n">
@@ -16294,7 +16306,7 @@
         <v>4</v>
       </c>
       <c r="AE90" t="n">
-        <v>4.242640687119285</v>
+        <v>4.242640687119284</v>
       </c>
       <c r="AF90" t="n">
         <v>2.75</v>
@@ -16379,7 +16391,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B91" t="n">
@@ -16470,7 +16482,7 @@
         <v>4.5</v>
       </c>
       <c r="AE91" t="n">
-        <v>4.203173404306163</v>
+        <v>4.203173404306162</v>
       </c>
       <c r="AF91" t="n">
         <v>3.125</v>
@@ -16555,7 +16567,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B92" t="n">
@@ -16731,7 +16743,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B93" t="n">
@@ -16822,7 +16834,7 @@
         <v>1.5</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.380476142847615</v>
+        <v>2.380476142847614</v>
       </c>
       <c r="AF93" t="n">
         <v>2.875</v>
@@ -16907,7 +16919,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B94" t="n">
@@ -16998,7 +17010,7 @@
         <v>1.5</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.380476142847615</v>
+        <v>2.380476142847614</v>
       </c>
       <c r="AF94" t="n">
         <v>2.75</v>
@@ -17083,7 +17095,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B95" t="n">
@@ -17174,7 +17186,7 @@
         <v>1.25</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.892969448600089</v>
+        <v>1.892969448600088</v>
       </c>
       <c r="AF95" t="n">
         <v>2.875</v>
@@ -17259,7 +17271,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B96" t="n">
@@ -17350,7 +17362,7 @@
         <v>1.25</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.892969448600089</v>
+        <v>1.892969448600088</v>
       </c>
       <c r="AF96" t="n">
         <v>2.5</v>
@@ -17435,7 +17447,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B97" t="n">
@@ -17526,7 +17538,7 @@
         <v>1</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.999999999999998</v>
+        <v>1.999999999999997</v>
       </c>
       <c r="AF97" t="n">
         <v>1.25</v>
@@ -17611,7 +17623,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="B98" t="n">
@@ -17702,7 +17714,7 @@
         <v>2.25</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.629955639676582</v>
+        <v>2.629955639676581</v>
       </c>
       <c r="AF98" t="n">
         <v>1.875</v>
@@ -17787,7 +17799,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B99" t="n">
@@ -17878,7 +17890,7 @@
         <v>1.25</v>
       </c>
       <c r="AE99" t="n">
-        <v>2.499999999999998</v>
+        <v>2.499999999999997</v>
       </c>
       <c r="AF99" t="n">
         <v>1.25</v>
@@ -17963,7 +17975,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45614</v>
       </c>
       <c r="B100" t="n">
@@ -18054,7 +18066,7 @@
         <v>1.25</v>
       </c>
       <c r="AE100" t="n">
-        <v>2.499999999999998</v>
+        <v>2.499999999999997</v>
       </c>
       <c r="AF100" t="n">
         <v>1.25</v>
@@ -18139,7 +18151,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45621</v>
       </c>
       <c r="B101" t="n">
@@ -18230,7 +18242,7 @@
         <v>1.5</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.380476142847615</v>
+        <v>2.380476142847614</v>
       </c>
       <c r="AF101" t="n">
         <v>1.25</v>
@@ -18315,7 +18327,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45628</v>
       </c>
       <c r="B102" t="n">
@@ -18491,7 +18503,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45635</v>
       </c>
       <c r="B103" t="n">
@@ -18582,7 +18594,7 @@
         <v>3.75</v>
       </c>
       <c r="AE103" t="n">
-        <v>3.774917217635374</v>
+        <v>3.774917217635373</v>
       </c>
       <c r="AF103" t="n">
         <v>2.5</v>
@@ -18667,7 +18679,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45642</v>
       </c>
       <c r="B104" t="n">
@@ -18758,7 +18770,7 @@
         <v>4.25</v>
       </c>
       <c r="AE104" t="n">
-        <v>3.201562118716423</v>
+        <v>3.201562118716422</v>
       </c>
       <c r="AF104" t="n">
         <v>2.75</v>
@@ -18843,7 +18855,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45649</v>
       </c>
       <c r="B105" t="n">
@@ -18934,7 +18946,7 @@
         <v>4.75</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.629955639676582</v>
+        <v>2.629955639676581</v>
       </c>
       <c r="AF105" t="n">
         <v>3.125</v>
@@ -19019,7 +19031,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45656</v>
       </c>
       <c r="B106" t="n">
@@ -19110,7 +19122,7 @@
         <v>3.75</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.217355782608343</v>
+        <v>2.217355782608342</v>
       </c>
       <c r="AF106" t="n">
         <v>2.875</v>
@@ -19195,7 +19207,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B107" t="n">
@@ -19286,7 +19298,7 @@
         <v>3.25</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.258305739211788</v>
+        <v>1.258305739211786</v>
       </c>
       <c r="AF107" t="n">
         <v>3.5</v>
@@ -19371,7 +19383,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="B108" t="n">
@@ -19462,7 +19474,7 @@
         <v>3.25</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.258305739211788</v>
+        <v>1.258305739211786</v>
       </c>
       <c r="AF108" t="n">
         <v>3.75</v>
@@ -19495,7 +19507,7 @@
         <v>4.25</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.5</v>
+        <v>1.500000000000002</v>
       </c>
       <c r="AQ108" t="n">
         <v>4.875</v>
@@ -19547,7 +19559,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B109" t="n">
@@ -19638,7 +19650,7 @@
         <v>2.75</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.70782512765993</v>
+        <v>1.707825127659929</v>
       </c>
       <c r="AF109" t="n">
         <v>3.75</v>
@@ -19671,7 +19683,7 @@
         <v>3.25</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.06155281280883</v>
+        <v>2.061552812808831</v>
       </c>
       <c r="AQ109" t="n">
         <v>4.875</v>
@@ -19723,7 +19735,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="B110" t="n">
@@ -19814,7 +19826,7 @@
         <v>2.5</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.732050807568875</v>
+        <v>1.732050807568873</v>
       </c>
       <c r="AF110" t="n">
         <v>3.125</v>
@@ -19847,7 +19859,7 @@
         <v>2.75</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659935</v>
       </c>
       <c r="AQ110" t="n">
         <v>4.375</v>
@@ -19899,7 +19911,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="B111" t="n">
@@ -19990,7 +20002,7 @@
         <v>1.25</v>
       </c>
       <c r="AE111" t="n">
-        <v>0.9574271077563333</v>
+        <v>0.9574271077563309</v>
       </c>
       <c r="AF111" t="n">
         <v>2.25</v>
@@ -20023,7 +20035,7 @@
         <v>1.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.290994448735806</v>
+        <v>1.290994448735807</v>
       </c>
       <c r="AQ111" t="n">
         <v>2.875</v>
@@ -20075,7 +20087,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B112" t="n">
@@ -20166,7 +20178,7 @@
         <v>1.25</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.9574271077563333</v>
+        <v>0.9574271077563309</v>
       </c>
       <c r="AF112" t="n">
         <v>2.25</v>
@@ -20199,7 +20211,7 @@
         <v>1.75</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.5</v>
+        <v>1.500000000000002</v>
       </c>
       <c r="AQ112" t="n">
         <v>3</v>
@@ -20251,7 +20263,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45705</v>
       </c>
       <c r="B113" t="n">
@@ -20427,7 +20439,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="B114" t="n">
@@ -20603,7 +20615,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="B115" t="n">
@@ -20727,7 +20739,7 @@
         <v>4.5</v>
       </c>
       <c r="AP115" t="n">
-        <v>5.744562646538029</v>
+        <v>5.74456264653803</v>
       </c>
       <c r="AQ115" t="n">
         <v>3</v>
@@ -20779,7 +20791,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="B116" t="n">
@@ -20903,7 +20915,7 @@
         <v>4.5</v>
       </c>
       <c r="AP116" t="n">
-        <v>5.744562646538029</v>
+        <v>5.74456264653803</v>
       </c>
       <c r="AQ116" t="n">
         <v>3.125</v>
@@ -20955,7 +20967,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45733</v>
       </c>
       <c r="B117" t="n">
@@ -21046,7 +21058,7 @@
         <v>1</v>
       </c>
       <c r="AE117" t="n">
-        <v>0.8164965809277213</v>
+        <v>0.8164965809277184</v>
       </c>
       <c r="AF117" t="n">
         <v>2.5</v>
@@ -21079,7 +21091,7 @@
         <v>1.25</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.25830573921179</v>
+        <v>1.258305739211794</v>
       </c>
       <c r="AQ117" t="n">
         <v>3</v>
@@ -21131,7 +21143,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="B118" t="n">
@@ -21222,7 +21234,7 @@
         <v>0.75</v>
       </c>
       <c r="AE118" t="n">
-        <v>0.957427107756334</v>
+        <v>0.9574271077563316</v>
       </c>
       <c r="AF118" t="n">
         <v>2.25</v>
@@ -21255,7 +21267,7 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.414213562373094</v>
+        <v>1.414213562373097</v>
       </c>
       <c r="AQ118" t="n">
         <v>2.625</v>
@@ -21307,7 +21319,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B119" t="n">
@@ -21398,7 +21410,7 @@
         <v>0.75</v>
       </c>
       <c r="AE119" t="n">
-        <v>0.957427107756334</v>
+        <v>0.9574271077563316</v>
       </c>
       <c r="AF119" t="n">
         <v>2.375</v>
@@ -21431,7 +21443,7 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.414213562373094</v>
+        <v>1.414213562373097</v>
       </c>
       <c r="AQ119" t="n">
         <v>2.75</v>
@@ -21483,7 +21495,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45754</v>
       </c>
       <c r="B120" t="n">
@@ -21574,7 +21586,7 @@
         <v>0.5</v>
       </c>
       <c r="AE120" t="n">
-        <v>0.577350269189619</v>
+        <v>0.5773502691896149</v>
       </c>
       <c r="AF120" t="n">
         <v>2.25</v>
@@ -21607,7 +21619,7 @@
         <v>0.5</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.577350269189623</v>
+        <v>0.5773502691896313</v>
       </c>
       <c r="AQ120" t="n">
         <v>2.5</v>
@@ -21659,7 +21671,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B121" t="n">
@@ -21750,7 +21762,7 @@
         <v>0.75</v>
       </c>
       <c r="AE121" t="n">
-        <v>0.4999999999999921</v>
+        <v>0.4999999999999873</v>
       </c>
       <c r="AF121" t="n">
         <v>0.875</v>
@@ -21783,7 +21795,7 @@
         <v>0.75</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.4999999999999968</v>
+        <v>0.5000000000000063</v>
       </c>
       <c r="AQ121" t="n">
         <v>1</v>
@@ -21835,7 +21847,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B122" t="n">
@@ -21860,19 +21872,19 @@
         <v>19.80025445292609</v>
       </c>
       <c r="I122" t="n">
-        <v>39.60050890585241</v>
+        <v>39.60050890586398</v>
       </c>
       <c r="J122" t="n">
         <v>9.900127226463217</v>
       </c>
       <c r="K122" t="n">
-        <v>28.00178838576651</v>
+        <v>28.00178838576197</v>
       </c>
       <c r="L122" t="n">
         <v>6.600084817642069</v>
       </c>
       <c r="M122" t="n">
-        <v>22.86336447684007</v>
+        <v>22.86336447683109</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
@@ -21926,7 +21938,7 @@
         <v>0.75</v>
       </c>
       <c r="AE122" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999873</v>
       </c>
       <c r="AF122" t="n">
         <v>0.75</v>
@@ -21959,7 +21971,7 @@
         <v>0.75</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000063</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.875</v>
@@ -22011,7 +22023,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="B123" t="n">
@@ -22036,19 +22048,19 @@
         <v>19.80025445292609</v>
       </c>
       <c r="I123" t="n">
-        <v>39.60050890585241</v>
+        <v>39.60050890586398</v>
       </c>
       <c r="J123" t="n">
         <v>9.900127226463217</v>
       </c>
       <c r="K123" t="n">
-        <v>28.00178838576651</v>
+        <v>28.00178838576197</v>
       </c>
       <c r="L123" t="n">
         <v>6.600084817642069</v>
       </c>
       <c r="M123" t="n">
-        <v>22.86336447684007</v>
+        <v>22.86336447683109</v>
       </c>
       <c r="N123" t="n">
         <v>1195.033078880407</v>
@@ -22102,7 +22114,7 @@
         <v>1.5</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.732050807568877</v>
+        <v>1.732050807568874</v>
       </c>
       <c r="AF123" t="n">
         <v>1.125</v>
@@ -22135,7 +22147,7 @@
         <v>1.75</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.217355782608345</v>
+        <v>2.217355782608347</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.375</v>
@@ -22187,7 +22199,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="B124" t="n">
@@ -22212,19 +22224,19 @@
         <v>44.75953047102564</v>
       </c>
       <c r="I124" t="n">
-        <v>52.36597591320189</v>
+        <v>52.36597591321045</v>
       </c>
       <c r="J124" t="n">
         <v>22.37976523551299</v>
       </c>
       <c r="K124" t="n">
-        <v>41.8046775168239</v>
+        <v>41.80467751682092</v>
       </c>
       <c r="L124" t="n">
         <v>14.91984349034192</v>
       </c>
       <c r="M124" t="n">
-        <v>35.1219017587411</v>
+        <v>35.12190175873535</v>
       </c>
       <c r="N124" t="n">
         <v>1487.171719457014</v>
@@ -22278,7 +22290,7 @@
         <v>2.75</v>
       </c>
       <c r="AE124" t="n">
-        <v>2.753785273643051</v>
+        <v>2.753785273643049</v>
       </c>
       <c r="AF124" t="n">
         <v>1.625</v>
@@ -22311,7 +22323,7 @@
         <v>3.25</v>
       </c>
       <c r="AP124" t="n">
-        <v>3.304037933599835</v>
+        <v>3.304037933599836</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.875</v>
@@ -22363,7 +22375,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="B125" t="n">
@@ -22388,19 +22400,19 @@
         <v>316.2295417832429</v>
       </c>
       <c r="I125" t="n">
-        <v>514.9016828016455</v>
+        <v>514.9016828016462</v>
       </c>
       <c r="J125" t="n">
         <v>158.1147708916216</v>
       </c>
       <c r="K125" t="n">
-        <v>377.0891283519775</v>
+        <v>377.0891283519772</v>
       </c>
       <c r="L125" t="n">
         <v>105.409847261081</v>
       </c>
       <c r="M125" t="n">
-        <v>310.7236261676349</v>
+        <v>310.7236261676344</v>
       </c>
       <c r="N125" t="n">
         <v>951.5991402714933</v>
@@ -22454,7 +22466,7 @@
         <v>3.75</v>
       </c>
       <c r="AE125" t="n">
-        <v>2.629955639676583</v>
+        <v>2.629955639676581</v>
       </c>
       <c r="AF125" t="n">
         <v>2.25</v>
@@ -22487,7 +22499,7 @@
         <v>4.5</v>
       </c>
       <c r="AP125" t="n">
-        <v>3.109126351029605</v>
+        <v>3.109126351029606</v>
       </c>
       <c r="AQ125" t="n">
         <v>2.625</v>
@@ -22539,7 +22551,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="B126" t="n">
@@ -22564,19 +22576,19 @@
         <v>296.4292873303167</v>
       </c>
       <c r="I126" t="n">
-        <v>528.4006152124259</v>
+        <v>528.4006152124266</v>
       </c>
       <c r="J126" t="n">
         <v>158.1147708916216</v>
       </c>
       <c r="K126" t="n">
-        <v>377.0891283519775</v>
+        <v>377.0891283519772</v>
       </c>
       <c r="L126" t="n">
         <v>105.409847261081</v>
       </c>
       <c r="M126" t="n">
-        <v>310.7236261676349</v>
+        <v>310.7236261676344</v>
       </c>
       <c r="N126" t="n">
         <v>1337.10407239819</v>
@@ -22630,7 +22642,7 @@
         <v>4.5</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.290994448735805</v>
+        <v>1.2909944487358</v>
       </c>
       <c r="AF126" t="n">
         <v>2.625</v>
@@ -22663,7 +22675,7 @@
         <v>5.25</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659935</v>
       </c>
       <c r="AQ126" t="n">
         <v>3</v>
@@ -22715,7 +22727,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="B127" t="n">
@@ -22740,19 +22752,19 @@
         <v>359.2107805429864</v>
       </c>
       <c r="I127" t="n">
-        <v>495.3240134249641</v>
+        <v>495.3240134249647</v>
       </c>
       <c r="J127" t="n">
         <v>189.5055174979565</v>
       </c>
       <c r="K127" t="n">
-        <v>372.4707555508817</v>
+        <v>372.4707555508814</v>
       </c>
       <c r="L127" t="n">
         <v>126.3370116653042</v>
       </c>
       <c r="M127" t="n">
-        <v>311.4347282094199</v>
+        <v>311.4347282094194</v>
       </c>
       <c r="N127" t="n">
         <v>1792.878280542987</v>
@@ -22806,7 +22818,7 @@
         <v>4.75</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.258305739211791</v>
+        <v>1.258305739211786</v>
       </c>
       <c r="AF127" t="n">
         <v>3.125</v>
@@ -22839,7 +22851,7 @@
         <v>6.25</v>
       </c>
       <c r="AP127" t="n">
-        <v>2.5</v>
+        <v>2.500000000000001</v>
       </c>
       <c r="AQ127" t="n">
         <v>4</v>
@@ -22891,7 +22903,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B128" t="n">
@@ -22916,19 +22928,19 @@
         <v>334.2515045248869</v>
       </c>
       <c r="I128" t="n">
-        <v>514.8797444715557</v>
+        <v>514.8797444715564</v>
       </c>
       <c r="J128" t="n">
         <v>189.5055174979565</v>
       </c>
       <c r="K128" t="n">
-        <v>372.4707555508817</v>
+        <v>372.4707555508814</v>
       </c>
       <c r="L128" t="n">
         <v>126.3370116653042</v>
       </c>
       <c r="M128" t="n">
-        <v>311.4347282094199</v>
+        <v>311.4347282094194</v>
       </c>
       <c r="N128" t="n">
         <v>1.087511312217195</v>
@@ -22982,7 +22994,7 @@
         <v>3.5</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.914854215512676</v>
+        <v>1.914854215512672</v>
       </c>
       <c r="AF128" t="n">
         <v>3.125</v>
@@ -23015,7 +23027,7 @@
         <v>5.25</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269015</v>
       </c>
       <c r="AQ128" t="n">
         <v>4.25</v>
@@ -23067,7 +23079,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B129" t="n">
@@ -23092,19 +23104,19 @@
         <v>147.600937657114</v>
       </c>
       <c r="I129" t="n">
-        <v>174.1929175224887</v>
+        <v>174.192917522491</v>
       </c>
       <c r="J129" t="n">
         <v>231.9152397201787</v>
       </c>
       <c r="K129" t="n">
-        <v>367.0873696430052</v>
+        <v>367.087369643005</v>
       </c>
       <c r="L129" t="n">
         <v>154.6101598134524</v>
       </c>
       <c r="M129" t="n">
-        <v>314.3098887411464</v>
+        <v>314.3098887411459</v>
       </c>
       <c r="N129" t="n">
         <v>913.022037037037</v>
@@ -23158,7 +23170,7 @@
         <v>3</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.632993161855451</v>
+        <v>1.632993161855448</v>
       </c>
       <c r="AF129" t="n">
         <v>3.375</v>
@@ -23191,7 +23203,7 @@
         <v>4.75</v>
       </c>
       <c r="AP129" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269015</v>
       </c>
       <c r="AQ129" t="n">
         <v>4.625</v>
@@ -23243,7 +23255,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B130" t="n">
@@ -23268,19 +23280,19 @@
         <v>203.007187657114</v>
       </c>
       <c r="I130" t="n">
-        <v>144.2724649141614</v>
+        <v>144.272464914164</v>
       </c>
       <c r="J130" t="n">
         <v>249.7182374937156</v>
       </c>
       <c r="K130" t="n">
-        <v>362.0419550041392</v>
+        <v>362.041955004139</v>
       </c>
       <c r="L130" t="n">
         <v>173.0789098134524</v>
       </c>
       <c r="M130" t="n">
-        <v>310.8918722195763</v>
+        <v>310.8918722195759</v>
       </c>
       <c r="N130" t="n">
         <v>2389.537037037037</v>
@@ -23334,7 +23346,7 @@
         <v>3.75</v>
       </c>
       <c r="AE130" t="n">
-        <v>2.217355782608345</v>
+        <v>2.217355782608342</v>
       </c>
       <c r="AF130" t="n">
         <v>4.125</v>
@@ -23367,7 +23379,7 @@
         <v>5.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.645751311064591</v>
+        <v>2.645751311064592</v>
       </c>
       <c r="AQ130" t="n">
         <v>5.375</v>
@@ -23419,7 +23431,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B131" t="n">
@@ -23444,19 +23456,19 @@
         <v>140.2256944444443</v>
       </c>
       <c r="I131" t="n">
-        <v>168.8925393942553</v>
+        <v>168.8925393942576</v>
       </c>
       <c r="J131" t="n">
         <v>249.7182374937156</v>
       </c>
       <c r="K131" t="n">
-        <v>362.0419550041392</v>
+        <v>362.041955004139</v>
       </c>
       <c r="L131" t="n">
         <v>173.0789098134524</v>
       </c>
       <c r="M131" t="n">
-        <v>310.8918722195763</v>
+        <v>310.8918722195759</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -23510,7 +23522,7 @@
         <v>2.5</v>
       </c>
       <c r="AE131" t="n">
-        <v>2.64575131106459</v>
+        <v>2.645751311064588</v>
       </c>
       <c r="AF131" t="n">
         <v>3.625</v>
@@ -23543,7 +23555,7 @@
         <v>3.25</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.5</v>
+        <v>2.500000000000001</v>
       </c>
       <c r="AQ131" t="n">
         <v>4.75</v>
@@ -23595,7 +23607,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B132" t="n">
@@ -23620,19 +23632,19 @@
         <v>484.955173611111</v>
       </c>
       <c r="I132" t="n">
-        <v>612.3494618746271</v>
+        <v>612.3494618746275</v>
       </c>
       <c r="J132" t="n">
         <v>409.6033390679992</v>
       </c>
       <c r="K132" t="n">
-        <v>529.9113451361221</v>
+        <v>529.911345136122</v>
       </c>
       <c r="L132" t="n">
         <v>287.9887362023413</v>
       </c>
       <c r="M132" t="n">
-        <v>460.1216737650603</v>
+        <v>460.1216737650601</v>
       </c>
       <c r="N132" t="n">
         <v>514.5256944444444</v>
@@ -23686,7 +23698,7 @@
         <v>3</v>
       </c>
       <c r="AE132" t="n">
-        <v>2.449489742783177</v>
+        <v>2.449489742783175</v>
       </c>
       <c r="AF132" t="n">
         <v>3.25</v>
@@ -23719,7 +23731,7 @@
         <v>3.25</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.5</v>
+        <v>2.500000000000001</v>
       </c>
       <c r="AQ132" t="n">
         <v>4.25</v>
@@ -23771,7 +23783,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B133" t="n">
@@ -23796,19 +23808,19 @@
         <v>867.7125632122506</v>
       </c>
       <c r="I133" t="n">
-        <v>901.2734368439118</v>
+        <v>901.273436843912</v>
       </c>
       <c r="J133" t="n">
         <v>507.6567504346825</v>
       </c>
       <c r="K133" t="n">
-        <v>713.6458153079282</v>
+        <v>713.645815307928</v>
       </c>
       <c r="L133" t="n">
         <v>443.8476808842026</v>
       </c>
       <c r="M133" t="n">
-        <v>636.619053592497</v>
+        <v>636.6190535924969</v>
       </c>
       <c r="N133" t="n">
         <v>1043.931623931624</v>
@@ -23862,7 +23874,7 @@
         <v>2.5</v>
       </c>
       <c r="AE133" t="n">
-        <v>2.64575131106459</v>
+        <v>2.645751311064588</v>
       </c>
       <c r="AF133" t="n">
         <v>2.75</v>
@@ -23895,7 +23907,7 @@
         <v>2.75</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.5</v>
+        <v>2.500000000000001</v>
       </c>
       <c r="AQ133" t="n">
         <v>3.75</v>
@@ -23947,7 +23959,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B134" t="n">
@@ -23972,7 +23984,7 @@
         <v>1024.460159366097</v>
       </c>
       <c r="I134" t="n">
-        <v>800.3203007075958</v>
+        <v>800.3203007075959</v>
       </c>
       <c r="J134" t="n">
         <v>613.7336735116056</v>
@@ -24038,7 +24050,7 @@
         <v>1.25</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.25830573921179</v>
+        <v>1.258305739211786</v>
       </c>
       <c r="AF134" t="n">
         <v>2.5</v>
@@ -24071,7 +24083,7 @@
         <v>1.5</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.290994448735805</v>
+        <v>1.290994448735807</v>
       </c>
       <c r="AQ134" t="n">
         <v>3.5</v>
@@ -24123,7 +24135,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B135" t="n">
@@ -24148,7 +24160,7 @@
         <v>1170.105458511396</v>
       </c>
       <c r="I135" t="n">
-        <v>572.2545873254447</v>
+        <v>572.254587325445</v>
       </c>
       <c r="J135" t="n">
         <v>655.1655764779204</v>
@@ -24214,7 +24226,7 @@
         <v>2.25</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.499999999999999</v>
+        <v>1.499999999999995</v>
       </c>
       <c r="AF135" t="n">
         <v>2.375</v>
@@ -24247,7 +24259,7 @@
         <v>2.75</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659934</v>
       </c>
       <c r="AQ135" t="n">
         <v>3</v>
@@ -24299,7 +24311,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B136" t="n">
@@ -24324,7 +24336,7 @@
         <v>919.9191417378916</v>
       </c>
       <c r="I136" t="n">
-        <v>662.2205314785105</v>
+        <v>662.2205314785107</v>
       </c>
       <c r="J136" t="n">
         <v>702.4371576745016</v>
@@ -24390,7 +24402,7 @@
         <v>1.75</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.499999999999999</v>
+        <v>1.499999999999995</v>
       </c>
       <c r="AF136" t="n">
         <v>2.375</v>
@@ -24423,7 +24435,7 @@
         <v>2.25</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.892969448600091</v>
+        <v>1.892969448600092</v>
       </c>
       <c r="AQ136" t="n">
         <v>2.75</v>
@@ -24475,7 +24487,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="B137" t="n">
@@ -24500,19 +24512,19 @@
         <v>453.7454415954415</v>
       </c>
       <c r="I137" t="n">
-        <v>355.4599236585971</v>
+        <v>355.4599236585976</v>
       </c>
       <c r="J137" t="n">
         <v>660.7290024038463</v>
       </c>
       <c r="K137" t="n">
-        <v>671.7433875928313</v>
+        <v>671.7433875928311</v>
       </c>
       <c r="L137" t="n">
         <v>489.6863141549354</v>
       </c>
       <c r="M137" t="n">
-        <v>599.3813627285581</v>
+        <v>599.381362728558</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -24566,7 +24578,7 @@
         <v>1.5</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.732050807568876</v>
+        <v>1.732050807568873</v>
       </c>
       <c r="AF137" t="n">
         <v>2</v>
@@ -24599,7 +24611,7 @@
         <v>1.75</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.217355782608345</v>
+        <v>2.217355782608346</v>
       </c>
       <c r="AQ137" t="n">
         <v>2.25</v>
@@ -24651,7 +24663,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B138" t="n">
@@ -24676,7 +24688,7 @@
         <v>241.5915954415953</v>
       </c>
       <c r="I138" t="n">
-        <v>288.0861607799058</v>
+        <v>288.0861607799063</v>
       </c>
       <c r="J138" t="n">
         <v>633.0258774038463</v>
@@ -24688,7 +24700,7 @@
         <v>489.6863141549355</v>
       </c>
       <c r="M138" t="n">
-        <v>599.3813627285581</v>
+        <v>599.381362728558</v>
       </c>
       <c r="N138" t="n">
         <v>916.0224089635853</v>
@@ -24742,7 +24754,7 @@
         <v>1.75</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.707825127659932</v>
+        <v>1.707825127659929</v>
       </c>
       <c r="AF138" t="n">
         <v>1.5</v>
@@ -24775,7 +24787,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.160246899469286</v>
+        <v>2.160246899469288</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.75</v>
@@ -24827,7 +24839,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45887</v>
       </c>
       <c r="B139" t="n">
@@ -24852,7 +24864,7 @@
         <v>95.9462962962962</v>
       </c>
       <c r="I139" t="n">
-        <v>188.1695036829771</v>
+        <v>188.1695036829779</v>
       </c>
       <c r="J139" t="n">
         <v>633.0258774038463</v>
@@ -24918,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="AE139" t="n">
-        <v>0.8164965809277238</v>
+        <v>0.8164965809277166</v>
       </c>
       <c r="AF139" t="n">
         <v>1.625</v>
@@ -24951,7 +24963,7 @@
         <v>1</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.8164965809277254</v>
+        <v>0.8164965809277281</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.875</v>
@@ -25003,7 +25015,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B140" t="n">
@@ -25028,13 +25040,13 @@
         <v>1.403133903133789</v>
       </c>
       <c r="I140" t="n">
-        <v>2.806267806297106</v>
+        <v>2.806267806352418</v>
       </c>
       <c r="J140" t="n">
         <v>460.6611378205129</v>
       </c>
       <c r="K140" t="n">
-        <v>654.9781932737964</v>
+        <v>654.9781932737963</v>
       </c>
       <c r="L140" t="n">
         <v>468.7591497507122</v>
@@ -25094,7 +25106,7 @@
         <v>0.75</v>
       </c>
       <c r="AE140" t="n">
-        <v>0.9574271077563362</v>
+        <v>0.9574271077563301</v>
       </c>
       <c r="AF140" t="n">
         <v>1.25</v>
@@ -25127,7 +25139,7 @@
         <v>0.75</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.9574271077563375</v>
+        <v>0.95742710775634</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.5</v>
@@ -25179,7 +25191,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B141" t="n">
@@ -25204,19 +25216,19 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
         <v>226.8727207977209</v>
       </c>
       <c r="K141" t="n">
-        <v>336.1175652143611</v>
+        <v>336.1175652143606</v>
       </c>
       <c r="L141" t="n">
         <v>440.4860016025641</v>
       </c>
       <c r="M141" t="n">
-        <v>626.8856468918926</v>
+        <v>626.8856468918925</v>
       </c>
       <c r="N141" t="n">
         <v>253.8375350140056</v>
@@ -25270,7 +25282,7 @@
         <v>1</v>
       </c>
       <c r="AE141" t="n">
-        <v>0.8164965809277238</v>
+        <v>0.8164965809277166</v>
       </c>
       <c r="AF141" t="n">
         <v>1.25</v>
@@ -25303,7 +25315,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.8164965809277254</v>
+        <v>0.8164965809277281</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.375</v>
@@ -25355,7 +25367,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="B142" t="n">
@@ -25380,13 +25392,13 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>120.7957977207978</v>
       </c>
       <c r="K142" t="n">
-        <v>228.5713099340423</v>
+        <v>228.5713099340416</v>
       </c>
       <c r="L142" t="n">
         <v>422.0172516025641</v>
@@ -25446,7 +25458,7 @@
         <v>1.5</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.732050807568876</v>
+        <v>1.732050807568873</v>
       </c>
       <c r="AF142" t="n">
         <v>1.625</v>
@@ -25479,7 +25491,7 @@
         <v>2</v>
       </c>
       <c r="AP142" t="n">
-        <v>2.70801280154532</v>
+        <v>2.708012801545321</v>
       </c>
       <c r="AQ142" t="n">
         <v>2</v>
@@ -25531,7 +25543,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45915</v>
       </c>
       <c r="B143" t="n">
@@ -25556,13 +25568,13 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
         <v>47.97314814814827</v>
       </c>
       <c r="K143" t="n">
-        <v>133.4352009108579</v>
+        <v>133.4352009108567</v>
       </c>
       <c r="L143" t="n">
         <v>422.0172516025641</v>
@@ -25622,7 +25634,7 @@
         <v>1.25</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.89296944860009</v>
+        <v>1.892969448600087</v>
       </c>
       <c r="AF143" t="n">
         <v>1.125</v>
@@ -25655,7 +25667,7 @@
         <v>1.75</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269015</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.375</v>
@@ -25707,7 +25719,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B144" t="n">
@@ -25732,19 +25744,19 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0.7015669515670653</v>
       </c>
       <c r="K144" t="n">
-        <v>1.984330995651681</v>
+        <v>1.984330995568911</v>
       </c>
       <c r="L144" t="n">
         <v>307.1074252136752</v>
       </c>
       <c r="M144" t="n">
-        <v>569.5983321108181</v>
+        <v>569.598332110818</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
@@ -25798,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.89296944860009</v>
+        <v>1.892969448600087</v>
       </c>
       <c r="AF144" t="n">
         <v>1</v>
@@ -25831,7 +25843,7 @@
         <v>1.75</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269015</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.25</v>
@@ -25883,7 +25895,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45929</v>
       </c>
       <c r="B145" t="n">
@@ -25908,19 +25920,19 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>151.2484805318139</v>
       </c>
       <c r="M145" t="n">
-        <v>290.4669814905437</v>
+        <v>290.4669814905434</v>
       </c>
       <c r="N145" t="n">
         <v>1487.978723404255</v>
@@ -25974,7 +25986,7 @@
         <v>1.75</v>
       </c>
       <c r="AE145" t="n">
-        <v>2.061552812808829</v>
+        <v>2.061552812808826</v>
       </c>
       <c r="AF145" t="n">
         <v>1.375</v>
@@ -26007,7 +26019,7 @@
         <v>2.25</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269015</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.625</v>
@@ -26059,7 +26071,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B146" t="n">
@@ -26084,19 +26096,19 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
         <v>80.53053181386515</v>
       </c>
       <c r="M146" t="n">
-        <v>191.7917680952425</v>
+        <v>191.7917680952418</v>
       </c>
       <c r="N146" t="n">
         <v>808.3827313904286</v>
@@ -26150,7 +26162,7 @@
         <v>1.5</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.732050807568876</v>
+        <v>1.732050807568873</v>
       </c>
       <c r="AF146" t="n">
         <v>1.5</v>
@@ -26183,7 +26195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.732050807568877</v>
+        <v>1.732050807568879</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.75</v>
@@ -26235,7 +26247,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="B147" t="n">
@@ -26260,19 +26272,19 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>31.9820987654321</v>
       </c>
       <c r="M147" t="n">
-        <v>109.0336885985655</v>
+        <v>109.0336885985642</v>
       </c>
       <c r="N147" t="n">
         <v>253.8375350140056</v>
@@ -26326,7 +26338,7 @@
         <v>1.75</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.499999999999999</v>
+        <v>1.499999999999995</v>
       </c>
       <c r="AF147" t="n">
         <v>1.5</v>
@@ -26359,7 +26371,7 @@
         <v>1.75</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.500000000000002</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.75</v>
@@ -26411,7 +26423,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B148" t="n">
@@ -26436,19 +26448,19 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
         <v>0.4677113010446344</v>
       </c>
       <c r="M148" t="n">
-        <v>1.62019947338922</v>
+        <v>1.620199473294087</v>
       </c>
       <c r="N148" t="n">
         <v>0</v>
@@ -26502,7 +26514,7 @@
         <v>1.75</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.499999999999999</v>
+        <v>1.499999999999995</v>
       </c>
       <c r="AF148" t="n">
         <v>1.5</v>
@@ -26535,7 +26547,7 @@
         <v>1.75</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.5</v>
+        <v>1.500000000000002</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.75</v>
@@ -26587,7 +26599,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B149" t="n">
@@ -26612,19 +26624,19 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
         <v>496.6386554621849</v>
@@ -26678,7 +26690,7 @@
         <v>1.25</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.25830573921179</v>
+        <v>1.258305739211785</v>
       </c>
       <c r="AF149" t="n">
         <v>1.5</v>
@@ -26711,7 +26723,7 @@
         <v>1.25</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.258305739211792</v>
+        <v>1.258305739211793</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.75</v>
@@ -26763,7 +26775,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="B150" t="n">
@@ -26788,19 +26800,19 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
         <v>0</v>
@@ -26854,7 +26866,7 @@
         <v>0.5</v>
       </c>
       <c r="AE150" t="n">
-        <v>0.5773502691896217</v>
+        <v>0.5773502691896115</v>
       </c>
       <c r="AF150" t="n">
         <v>1</v>
@@ -26887,7 +26899,7 @@
         <v>0.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.5773502691896253</v>
+        <v>0.5773502691896294</v>
       </c>
       <c r="AQ150" t="n">
         <v>1</v>
@@ -26939,7 +26951,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="B151" t="n">
@@ -26964,19 +26976,19 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
         <v>0</v>
@@ -27030,7 +27042,7 @@
         <v>0.25</v>
       </c>
       <c r="AE151" t="n">
-        <v>0.4999999999999953</v>
+        <v>0.4999999999999835</v>
       </c>
       <c r="AF151" t="n">
         <v>1</v>
@@ -27063,7 +27075,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.4999999999999995</v>
+        <v>0.5000000000000042</v>
       </c>
       <c r="AQ151" t="n">
         <v>1</v>
@@ -27115,7 +27127,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B152" t="n">
@@ -27140,19 +27152,19 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
         <v>2592.105263157895</v>
@@ -27206,7 +27218,7 @@
         <v>1.25</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.89296944860009</v>
+        <v>1.892969448600087</v>
       </c>
       <c r="AF152" t="n">
         <v>1.5</v>
@@ -27291,7 +27303,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="B153" t="n">
@@ -27316,19 +27328,19 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -27382,7 +27394,7 @@
         <v>1</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.999999999999999</v>
+        <v>1.999999999999996</v>
       </c>
       <c r="AF153" t="n">
         <v>1.125</v>
@@ -27415,7 +27427,7 @@
         <v>1.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>3.5</v>
+        <v>3.500000000000001</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.5</v>
@@ -27467,7 +27479,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B154" t="n">
@@ -27492,19 +27504,19 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
         <v>0</v>
@@ -27558,7 +27570,7 @@
         <v>1</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.999999999999999</v>
+        <v>1.999999999999996</v>
       </c>
       <c r="AF154" t="n">
         <v>0.75</v>
@@ -27591,7 +27603,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154" t="n">
-        <v>3.5</v>
+        <v>3.500000000000001</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.125</v>
@@ -27643,7 +27655,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B155" t="n">
@@ -27668,19 +27680,19 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
         <v>1572.999620596206</v>
@@ -27734,7 +27746,7 @@
         <v>2</v>
       </c>
       <c r="AE155" t="n">
-        <v>2.309401076758502</v>
+        <v>2.309401076758499</v>
       </c>
       <c r="AF155" t="n">
         <v>1.125</v>
@@ -27819,7 +27831,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46006</v>
       </c>
       <c r="B156" t="n">
@@ -27844,19 +27856,19 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
         <v>1345.365853658537</v>
@@ -27910,7 +27922,7 @@
         <v>1.5</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.914854215512675</v>
+        <v>1.914854215512672</v>
       </c>
       <c r="AF156" t="n">
         <v>1.375</v>
@@ -27943,7 +27955,7 @@
         <v>2.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>3.3166247903554</v>
+        <v>3.316624790355401</v>
       </c>
       <c r="AQ156" t="n">
         <v>2.25</v>
@@ -27995,7 +28007,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B157" t="n">
@@ -28020,19 +28032,19 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
         <v>234.9051490514905</v>
@@ -28086,7 +28098,7 @@
         <v>1.75</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.707825127659932</v>
+        <v>1.707825127659928</v>
       </c>
       <c r="AF157" t="n">
         <v>1.375</v>
@@ -28171,7 +28183,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B158" t="n">
@@ -28196,19 +28208,19 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
         <v>487.1078590785907</v>
@@ -28262,7 +28274,7 @@
         <v>2.75</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.499999999999998</v>
+        <v>1.499999999999994</v>
       </c>
       <c r="AF158" t="n">
         <v>1.875</v>
@@ -28295,7 +28307,7 @@
         <v>4.75</v>
       </c>
       <c r="AP158" t="n">
-        <v>3.304037933599835</v>
+        <v>3.304037933599836</v>
       </c>
       <c r="AQ158" t="n">
         <v>3.25</v>
@@ -28347,7 +28359,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="B159" t="n">
@@ -28372,19 +28384,19 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
@@ -28438,7 +28450,7 @@
         <v>1.75</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.707825127659932</v>
+        <v>1.707825127659928</v>
       </c>
       <c r="AF159" t="n">
         <v>1.875</v>
@@ -28471,7 +28483,7 @@
         <v>3</v>
       </c>
       <c r="AP159" t="n">
-        <v>3.559026084010437</v>
+        <v>3.559026084010438</v>
       </c>
       <c r="AQ159" t="n">
         <v>3.25</v>
@@ -28523,7 +28535,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="B160" t="n">
@@ -28548,19 +28560,19 @@
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
@@ -28614,7 +28626,7 @@
         <v>1.25</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.89296944860009</v>
+        <v>1.892969448600087</v>
       </c>
       <c r="AF160" t="n">
         <v>1.375</v>
@@ -28647,7 +28659,7 @@
         <v>2.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>3.862210075418822</v>
+        <v>3.862210075418823</v>
       </c>
       <c r="AQ160" t="n">
         <v>2.375</v>
@@ -28699,7 +28711,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="B161" t="n">
@@ -28724,19 +28736,19 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
         <v>738.1002638522427</v>
@@ -28790,7 +28802,7 @@
         <v>1.25</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.89296944860009</v>
+        <v>1.892969448600087</v>
       </c>
       <c r="AF161" t="n">
         <v>1.5</v>
@@ -28823,7 +28835,7 @@
         <v>2.5</v>
       </c>
       <c r="AP161" t="n">
-        <v>3.785938897200182</v>
+        <v>3.785938897200183</v>
       </c>
       <c r="AQ161" t="n">
         <v>2.625</v>
@@ -28875,7 +28887,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="B162" t="n">
@@ -28900,19 +28912,19 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
         <v>2653.678364116095</v>
@@ -28966,7 +28978,7 @@
         <v>1.75</v>
       </c>
       <c r="AE162" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269012</v>
       </c>
       <c r="AF162" t="n">
         <v>2.25</v>
@@ -28999,7 +29011,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.82842712474619</v>
+        <v>2.828427124746191</v>
       </c>
       <c r="AQ162" t="n">
         <v>3.375</v>
@@ -29051,7 +29063,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B163" t="n">
@@ -29076,19 +29088,19 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
         <v>0</v>
@@ -29142,7 +29154,7 @@
         <v>1.75</v>
       </c>
       <c r="AE163" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269012</v>
       </c>
       <c r="AF163" t="n">
         <v>1.75</v>
@@ -29175,7 +29187,7 @@
         <v>2</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.82842712474619</v>
+        <v>2.828427124746191</v>
       </c>
       <c r="AQ163" t="n">
         <v>2.5</v>
@@ -29227,7 +29239,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B164" t="n">
@@ -29252,19 +29264,19 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
         <v>0</v>
@@ -29318,7 +29330,7 @@
         <v>1.75</v>
       </c>
       <c r="AE164" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269012</v>
       </c>
       <c r="AF164" t="n">
         <v>1.5</v>
@@ -29351,7 +29363,7 @@
         <v>2</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.82842712474619</v>
+        <v>2.828427124746191</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.125</v>
@@ -29403,7 +29415,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B165" t="n">
@@ -29428,19 +29440,19 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
         <v>524.3532338308459</v>
@@ -29494,7 +29506,7 @@
         <v>1.75</v>
       </c>
       <c r="AE165" t="n">
-        <v>2.872281323269014</v>
+        <v>2.872281323269012</v>
       </c>
       <c r="AF165" t="n">
         <v>1.5</v>
@@ -29579,7 +29591,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="B166" t="n">
@@ -29604,19 +29616,19 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
         <v>5.939402985074627</v>
@@ -29670,7 +29682,7 @@
         <v>0.5</v>
       </c>
       <c r="AE166" t="n">
-        <v>0.5773502691896231</v>
+        <v>0.5773502691896127</v>
       </c>
       <c r="AF166" t="n">
         <v>1.125</v>
@@ -29703,7 +29715,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166" t="n">
-        <v>0.5773502691896262</v>
+        <v>0.5773502691896303</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.25</v>
@@ -29755,7 +29767,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="B167" t="n">
@@ -29780,19 +29792,19 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
         <v>509.6517412935324</v>
@@ -29846,7 +29858,7 @@
         <v>1</v>
       </c>
       <c r="AE167" t="n">
-        <v>0.8164965809277241</v>
+        <v>0.8164965809277169</v>
       </c>
       <c r="AF167" t="n">
         <v>1.375</v>
@@ -29879,7 +29891,7 @@
         <v>1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.8164965809277264</v>
+        <v>0.8164965809277293</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.5</v>
@@ -29931,7 +29943,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46090</v>
       </c>
       <c r="B168" t="n">
@@ -29956,19 +29968,19 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
         <v>226.8804793028322</v>
@@ -30022,7 +30034,7 @@
         <v>1.75</v>
       </c>
       <c r="AE168" t="n">
-        <v>0.9574271077563365</v>
+        <v>0.9574271077563303</v>
       </c>
       <c r="AF168" t="n">
         <v>1.75</v>
@@ -30055,7 +30067,7 @@
         <v>2</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.414213562373095</v>
+        <v>1.414213562373097</v>
       </c>
       <c r="AQ168" t="n">
         <v>2</v>
@@ -30107,7 +30119,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B169" t="n">
@@ -30132,19 +30144,19 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
         <v>0</v>
@@ -30198,7 +30210,7 @@
         <v>1.5</v>
       </c>
       <c r="AE169" t="n">
-        <v>1.290994448735804</v>
+        <v>1.2909944487358</v>
       </c>
       <c r="AF169" t="n">
         <v>1.625</v>
@@ -30231,7 +30243,7 @@
         <v>1.75</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659935</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.75</v>
@@ -30283,7 +30295,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="B170" t="n">
@@ -30308,19 +30320,19 @@
         <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
         <v>2.31764705882353</v>
@@ -30374,7 +30386,7 @@
         <v>1.75</v>
       </c>
       <c r="AE170" t="n">
-        <v>1.25830573921179</v>
+        <v>1.258305739211786</v>
       </c>
       <c r="AF170" t="n">
         <v>1.125</v>
@@ -30407,7 +30419,7 @@
         <v>2.5</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.914854215512676</v>
+        <v>1.914854215512678</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.5</v>
@@ -30459,7 +30471,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="B171" t="n">
@@ -30484,19 +30496,19 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
         <v>729.6296296296296</v>
@@ -30550,7 +30562,7 @@
         <v>1.5</v>
       </c>
       <c r="AE171" t="n">
-        <v>1.290994448735804</v>
+        <v>1.2909944487358</v>
       </c>
       <c r="AF171" t="n">
         <v>1.25</v>
@@ -30583,7 +30595,7 @@
         <v>2.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.06155281280883</v>
+        <v>2.061552812808832</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.625</v>
@@ -30635,7 +30647,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="B172" t="n">
@@ -30660,19 +30672,19 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
         <v>0</v>
@@ -30726,7 +30738,7 @@
         <v>0.75</v>
       </c>
       <c r="AE172" t="n">
-        <v>0.9574271077563365</v>
+        <v>0.9574271077563303</v>
       </c>
       <c r="AF172" t="n">
         <v>1.25</v>
@@ -30759,7 +30771,7 @@
         <v>1.25</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.892969448600091</v>
+        <v>1.892969448600093</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.625</v>
@@ -30811,7 +30823,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="B173" t="n">
@@ -30836,19 +30848,19 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
         <v>0</v>
@@ -30902,7 +30914,7 @@
         <v>0.75</v>
       </c>
       <c r="AE173" t="n">
-        <v>0.9574271077563365</v>
+        <v>0.9574271077563303</v>
       </c>
       <c r="AF173" t="n">
         <v>1.125</v>
@@ -30935,7 +30947,7 @@
         <v>1.25</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.892969448600091</v>
+        <v>1.892969448600093</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.5</v>
@@ -30987,7 +30999,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="B174" t="n">
@@ -31012,19 +31024,19 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
         <v>1469.752808988764</v>
@@ -31078,7 +31090,7 @@
         <v>1</v>
       </c>
       <c r="AE174" t="n">
-        <v>1.414213562373094</v>
+        <v>1.41421356237309</v>
       </c>
       <c r="AF174" t="n">
         <v>1.375</v>
@@ -31111,7 +31123,7 @@
         <v>1</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.414213562373096</v>
+        <v>1.414213562373097</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.75</v>
@@ -31163,7 +31175,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B175" t="n">
@@ -31188,19 +31200,19 @@
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
         <v>586.8386516853933</v>
@@ -31254,7 +31266,7 @@
         <v>1.75</v>
       </c>
       <c r="AE175" t="n">
-        <v>2.06155281280883</v>
+        <v>2.061552812808827</v>
       </c>
       <c r="AF175" t="n">
         <v>1.625</v>
@@ -31287,7 +31299,7 @@
         <v>1.75</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.06155281280883</v>
+        <v>2.061552812808832</v>
       </c>
       <c r="AQ175" t="n">
         <v>2</v>
@@ -31339,7 +31351,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B176" t="n">
@@ -31364,19 +31376,19 @@
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
         <v>2.124943820224719</v>
@@ -31430,7 +31442,7 @@
         <v>2.25</v>
       </c>
       <c r="AE176" t="n">
-        <v>1.707825127659932</v>
+        <v>1.707825127659929</v>
       </c>
       <c r="AF176" t="n">
         <v>1.5</v>
@@ -31463,7 +31475,7 @@
         <v>2.75</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.892969448600091</v>
+        <v>1.892969448600093</v>
       </c>
       <c r="AQ176" t="n">
         <v>2</v>
@@ -31515,7 +31527,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B177" t="n">
@@ -31540,19 +31552,19 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
         <v>322.1</v>
@@ -31606,7 +31618,7 @@
         <v>2.75</v>
       </c>
       <c r="AE177" t="n">
-        <v>0.9574271077563365</v>
+        <v>0.9574271077563303</v>
       </c>
       <c r="AF177" t="n">
         <v>1.75</v>
@@ -31639,7 +31651,7 @@
         <v>3.25</v>
       </c>
       <c r="AP177" t="n">
-        <v>0.9574271077563389</v>
+        <v>0.9574271077563413</v>
       </c>
       <c r="AQ177" t="n">
         <v>2.25</v>
@@ -31691,7 +31703,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B178" t="n">
@@ -31716,19 +31728,19 @@
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
         <v>910</v>
@@ -31782,7 +31794,7 @@
         <v>2.5</v>
       </c>
       <c r="AE178" t="n">
-        <v>0.9999999999999984</v>
+        <v>0.9999999999999926</v>
       </c>
       <c r="AF178" t="n">
         <v>1.75</v>
@@ -31815,7 +31827,7 @@
         <v>3.25</v>
       </c>
       <c r="AP178" t="n">
-        <v>0.9574271077563389</v>
+        <v>0.9574271077563413</v>
       </c>
       <c r="AQ178" t="n">
         <v>2.125</v>
@@ -31867,7 +31879,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="B179" t="n">
@@ -31892,19 +31904,19 @@
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>1.28297757551834e-05</v>
+        <v>0</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>7.511975870734047e-06</v>
+        <v>0</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>8.509318623460672e-06</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
         <v>0</v>
@@ -31958,7 +31970,7 @@
         <v>1.5</v>
       </c>
       <c r="AE179" t="n">
-        <v>1</v>
+        <v>0.9999999999999926</v>
       </c>
       <c r="AF179" t="n">
         <v>1.625</v>
@@ -31991,7 +32003,7 @@
         <v>2.25</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.707825127659933</v>
+        <v>1.707825127659935</v>
       </c>
       <c r="AQ179" t="n">
         <v>2</v>
@@ -32057,17 +32069,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -33074,12 +33086,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metrica</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/input/dataset_modelado_semanal.xlsx
+++ b/input/dataset_modelado_semanal.xlsx
@@ -680,37 +680,37 @@
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>exog_nacimientos_indice_semanal</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
           <t>exog_semana_anio_sin</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>exog_semana_anio_cos</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>exog_mes_sin</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>exog_mes_cos</t>
         </is>
       </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>exog_nacimientos_indice_publicado_lag_1s</t>
+        </is>
+      </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>exog_inpc_publicado</t>
+          <t>exog_inpc_publicado_lag_1s</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>exog_temperatura_lag_1s</t>
+          <t>exog_temperatura_publicado_lag_1s</t>
         </is>
       </c>
     </row>
@@ -869,19 +869,19 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>96.3</v>
+        <v>0.120536680255323</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.120536680255323</v>
+        <v>0.992708874098054</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.992708874098054</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.8660254037844387</v>
+        <v>99.47142857142856</v>
       </c>
       <c r="BE2" t="n">
         <v>7.91</v>
@@ -1045,19 +1045,19 @@
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
+        <v>0.2393156642875577</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD3" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.2393156642875577</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE3" t="n">
         <v>7.91</v>
@@ -1221,19 +1221,19 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD4" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE4" t="n">
         <v>7.91</v>
@@ -1397,19 +1397,19 @@
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
+        <v>0.4647231720437685</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD5" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.4647231720437685</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE5" t="n">
         <v>7.91</v>
@@ -1573,19 +1573,19 @@
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD6" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE6" t="n">
         <v>7.91</v>
@@ -1749,19 +1749,19 @@
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD7" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE7" t="n">
         <v>7.62</v>
@@ -1925,19 +1925,19 @@
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.6631226582407953</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD8" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.6631226582407953</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE8" t="n">
         <v>7.62</v>
@@ -2101,19 +2101,19 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.5680647467311559</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD9" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.5680647467311559</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE9" t="n">
         <v>7.62</v>
@@ -2277,19 +2277,19 @@
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.4647231720437686</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD10" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0.4647231720437686</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE10" t="n">
         <v>7.62</v>
@@ -2453,19 +2453,19 @@
         <v>0</v>
       </c>
       <c r="AZ11" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD11" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE11" t="n">
         <v>6.85</v>
@@ -2629,19 +2629,19 @@
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.239315664287558</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD12" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.239315664287558</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE12" t="n">
         <v>6.85</v>
@@ -2805,19 +2805,19 @@
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.120536680255323</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD13" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0.120536680255323</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE13" t="n">
         <v>6.85</v>
@@ -2981,19 +2981,19 @@
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-1.608122649676637e-16</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD14" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-1.608122649676637e-16</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE14" t="n">
         <v>6.85</v>
@@ -3157,19 +3157,19 @@
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.1205366802553229</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD15" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0.1205366802553229</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE15" t="n">
         <v>6.25</v>
@@ -3333,19 +3333,19 @@
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
+        <v>0.9709418174260521</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.2393156642875575</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD16" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0.9709418174260521</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>-0.2393156642875575</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE16" t="n">
         <v>6.25</v>
@@ -3509,19 +3509,19 @@
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.3546048870425355</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD17" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-0.3546048870425355</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE17" t="n">
         <v>6.25</v>
@@ -3685,19 +3685,19 @@
         <v>0</v>
       </c>
       <c r="AZ18" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.4647231720437685</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD18" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-0.4647231720437685</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE18" t="n">
         <v>6.25</v>
@@ -3861,19 +3861,19 @@
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
+        <v>0.8229838658936565</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.5680647467311557</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD19" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.8229838658936565</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-0.5680647467311557</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE19" t="n">
         <v>6.25</v>
@@ -4037,19 +4037,19 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
+        <v>0.7485107481711013</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD20" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0.7485107481711013</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE20" t="n">
         <v>5.84</v>
@@ -4213,19 +4213,19 @@
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.7485107481711012</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD21" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>-0.7485107481711012</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE21" t="n">
         <v>5.84</v>
@@ -4389,19 +4389,19 @@
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD22" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE22" t="n">
         <v>5.84</v>
@@ -4565,19 +4565,19 @@
         <v>0</v>
       </c>
       <c r="AZ23" t="n">
+        <v>0.4647231720437691</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD23" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0.4647231720437691</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE23" t="n">
         <v>5.84</v>
@@ -4741,19 +4741,19 @@
         <v>0</v>
       </c>
       <c r="AZ24" t="n">
+        <v>0.3546048870425358</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>-0.9350162426854147</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD24" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0.3546048870425358</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>-0.9350162426854147</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>-1</v>
       </c>
       <c r="BE24" t="n">
         <v>5.06</v>
@@ -4917,19 +4917,19 @@
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
+        <v>0.2393156642875577</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>-0.970941817426052</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD25" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0.2393156642875577</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>-0.970941817426052</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>-1</v>
       </c>
       <c r="BE25" t="n">
         <v>5.06</v>
@@ -5093,19 +5093,19 @@
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
+        <v>0.1205366802553231</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD26" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0.1205366802553231</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>-1</v>
       </c>
       <c r="BE26" t="n">
         <v>5.06</v>
@@ -5269,19 +5269,19 @@
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
+        <v>-3.216245299353273e-16</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD27" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>-3.216245299353273e-16</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>-1</v>
       </c>
       <c r="BE27" t="n">
         <v>5.06</v>
@@ -5445,19 +5445,19 @@
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
+        <v>-0.1205366802553228</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD28" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>-0.1205366802553228</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE28" t="n">
         <v>4.79</v>
@@ -5621,19 +5621,19 @@
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
+        <v>-0.2393156642875574</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>-0.9709418174260521</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD29" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>-0.2393156642875574</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>-0.9709418174260521</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE29" t="n">
         <v>4.79</v>
@@ -5797,19 +5797,19 @@
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
+        <v>-0.3546048870425356</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>-0.9350162426854148</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD30" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>-0.3546048870425356</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>-0.9350162426854148</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE30" t="n">
         <v>4.79</v>
@@ -5973,19 +5973,19 @@
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
+        <v>-0.4647231720437681</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>-0.8854560256532101</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD31" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>-0.4647231720437681</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>-0.8854560256532101</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE31" t="n">
         <v>4.79</v>
@@ -6149,19 +6149,19 @@
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
+        <v>-0.5680647467311556</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>-0.8229838658936566</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD32" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>-0.5680647467311556</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>-0.8229838658936566</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE32" t="n">
         <v>4.79</v>
@@ -6325,19 +6325,19 @@
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>-0.7485107481711013</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD33" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>-0.7485107481711013</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE33" t="n">
         <v>4.64</v>
@@ -6501,19 +6501,19 @@
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
+        <v>-0.7485107481711011</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>-0.6631226582407952</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD34" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>-0.7485107481711011</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>-0.6631226582407952</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE34" t="n">
         <v>4.64</v>
@@ -6677,19 +6677,19 @@
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>-0.5680647467311559</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD35" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>-0.5680647467311559</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE35" t="n">
         <v>4.64</v>
@@ -6853,19 +6853,19 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>-0.4647231720437691</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD36" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>-0.4647231720437691</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE36" t="n">
         <v>4.64</v>
@@ -7029,19 +7029,19 @@
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
+        <v>-0.9350162426854147</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>-0.3546048870425359</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD37" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>-0.9350162426854147</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>-0.3546048870425359</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE37" t="n">
         <v>4.45</v>
@@ -7205,19 +7205,19 @@
         <v>0</v>
       </c>
       <c r="AZ38" t="n">
+        <v>-0.970941817426052</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>-0.2393156642875577</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD38" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>-0.970941817426052</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>-0.2393156642875577</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE38" t="n">
         <v>4.45</v>
@@ -7381,19 +7381,19 @@
         <v>0</v>
       </c>
       <c r="AZ39" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>-0.1205366802553236</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD39" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>-0.1205366802553236</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE39" t="n">
         <v>4.45</v>
@@ -7557,19 +7557,19 @@
         <v>0</v>
       </c>
       <c r="AZ40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD40" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>-1.83697019872103e-16</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE40" t="n">
         <v>4.45</v>
@@ -7733,19 +7733,19 @@
         <v>0</v>
       </c>
       <c r="AZ41" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0.1205366802553232</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD41" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0.1205366802553232</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE41" t="n">
         <v>4.26</v>
@@ -7909,19 +7909,19 @@
         <v>0</v>
       </c>
       <c r="AZ42" t="n">
+        <v>-0.9709418174260521</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0.2393156642875574</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD42" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>-0.9709418174260521</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0.2393156642875574</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE42" t="n">
         <v>4.26</v>
@@ -8085,19 +8085,19 @@
         <v>0</v>
       </c>
       <c r="AZ43" t="n">
+        <v>-0.9350162426854148</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD43" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>-0.9350162426854148</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE43" t="n">
         <v>4.26</v>
@@ -8261,19 +8261,19 @@
         <v>0</v>
       </c>
       <c r="AZ44" t="n">
+        <v>-0.8854560256532101</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0.464723172043768</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD44" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>-0.8854560256532101</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>0.464723172043768</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE44" t="n">
         <v>4.26</v>
@@ -8437,19 +8437,19 @@
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
+        <v>-0.822983865893657</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0.5680647467311548</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD45" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>-0.822983865893657</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0.5680647467311548</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE45" t="n">
         <v>4.26</v>
@@ -8613,19 +8613,19 @@
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
+        <v>-0.7485107481711011</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD46" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>-0.7485107481711011</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE46" t="n">
         <v>4.32</v>
@@ -8789,19 +8789,19 @@
         <v>0</v>
       </c>
       <c r="AZ47" t="n">
+        <v>-0.6631226582407955</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0.7485107481711007</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD47" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>-0.6631226582407955</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>0.7485107481711007</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE47" t="n">
         <v>4.32</v>
@@ -8965,19 +8965,19 @@
         <v>0</v>
       </c>
       <c r="AZ48" t="n">
+        <v>-0.5680647467311559</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD48" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>-0.5680647467311559</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE48" t="n">
         <v>4.32</v>
@@ -9141,19 +9141,19 @@
         <v>0</v>
       </c>
       <c r="AZ49" t="n">
+        <v>-0.4647231720437684</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0.88545602565321</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD49" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>-0.4647231720437684</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>0.88545602565321</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE49" t="n">
         <v>4.32</v>
@@ -9317,19 +9317,19 @@
         <v>0</v>
       </c>
       <c r="AZ50" t="n">
+        <v>-0.354604887042536</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0.9350162426854147</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD50" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>-0.354604887042536</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>0.9350162426854147</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>1</v>
       </c>
       <c r="BE50" t="n">
         <v>4.66</v>
@@ -9493,19 +9493,19 @@
         <v>0</v>
       </c>
       <c r="AZ51" t="n">
+        <v>-0.2393156642875578</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD51" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>-0.2393156642875578</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>1</v>
       </c>
       <c r="BE51" t="n">
         <v>4.66</v>
@@ -9669,19 +9669,19 @@
         <v>0</v>
       </c>
       <c r="AZ52" t="n">
+        <v>-0.1205366802553236</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD52" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>-0.1205366802553236</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>1</v>
       </c>
       <c r="BE52" t="n">
         <v>4.66</v>
@@ -9845,19 +9845,19 @@
         <v>0</v>
       </c>
       <c r="AZ53" t="n">
+        <v>6.432490598706546e-16</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD53" t="n">
         <v>96.3</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>6.432490598706546e-16</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>1</v>
       </c>
       <c r="BE53" t="n">
         <v>4.66</v>
@@ -10021,19 +10021,19 @@
         <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>88.40000000000001</v>
+        <v>0.120536680255323</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.120536680255323</v>
+        <v>0.992708874098054</v>
       </c>
       <c r="BB54" t="n">
-        <v>0.992708874098054</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="BD54" t="n">
-        <v>0.8660254037844387</v>
+        <v>96.3</v>
       </c>
       <c r="BE54" t="n">
         <v>4.66</v>
@@ -10197,19 +10197,19 @@
         <v>0</v>
       </c>
       <c r="AZ55" t="n">
+        <v>0.2393156642875577</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD55" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0.2393156642875577</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE55" t="n">
         <v>4.88</v>
@@ -10373,19 +10373,19 @@
         <v>0</v>
       </c>
       <c r="AZ56" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD56" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE56" t="n">
         <v>4.88</v>
@@ -10549,19 +10549,19 @@
         <v>0</v>
       </c>
       <c r="AZ57" t="n">
+        <v>0.4647231720437685</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD57" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0.4647231720437685</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE57" t="n">
         <v>4.88</v>
@@ -10725,19 +10725,19 @@
         <v>0</v>
       </c>
       <c r="AZ58" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD58" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE58" t="n">
         <v>4.88</v>
@@ -10901,19 +10901,19 @@
         <v>0</v>
       </c>
       <c r="AZ59" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD59" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE59" t="n">
         <v>4.4</v>
@@ -11077,19 +11077,19 @@
         <v>0</v>
       </c>
       <c r="AZ60" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0.6631226582407953</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD60" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>0.6631226582407953</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE60" t="n">
         <v>4.4</v>
@@ -11253,19 +11253,19 @@
         <v>0</v>
       </c>
       <c r="AZ61" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0.5680647467311559</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD61" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>0.5680647467311559</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE61" t="n">
         <v>4.4</v>
@@ -11429,19 +11429,19 @@
         <v>0</v>
       </c>
       <c r="AZ62" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0.4647231720437686</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD62" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>0.4647231720437686</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE62" t="n">
         <v>4.4</v>
@@ -11605,19 +11605,19 @@
         <v>0</v>
       </c>
       <c r="AZ63" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD63" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE63" t="n">
         <v>4.42</v>
@@ -11781,19 +11781,19 @@
         <v>0</v>
       </c>
       <c r="AZ64" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0.239315664287558</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD64" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>0.239315664287558</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE64" t="n">
         <v>4.42</v>
@@ -11957,19 +11957,19 @@
         <v>0</v>
       </c>
       <c r="AZ65" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0.120536680255323</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD65" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>0.120536680255323</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE65" t="n">
         <v>4.42</v>
@@ -12133,19 +12133,19 @@
         <v>0</v>
       </c>
       <c r="AZ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>-1.608122649676637e-16</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD66" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>-1.608122649676637e-16</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE66" t="n">
         <v>4.42</v>
@@ -12309,19 +12309,19 @@
         <v>0</v>
       </c>
       <c r="AZ67" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>-0.1205366802553229</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD67" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>-0.1205366802553229</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE67" t="n">
         <v>4.42</v>
@@ -12485,19 +12485,19 @@
         <v>0</v>
       </c>
       <c r="AZ68" t="n">
+        <v>0.9709418174260521</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>-0.2393156642875575</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD68" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>0.9709418174260521</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>-0.2393156642875575</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE68" t="n">
         <v>4.65</v>
@@ -12661,19 +12661,19 @@
         <v>0</v>
       </c>
       <c r="AZ69" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>-0.3546048870425355</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD69" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA69" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB69" t="n">
-        <v>-0.3546048870425355</v>
-      </c>
-      <c r="BC69" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD69" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE69" t="n">
         <v>4.65</v>
@@ -12837,19 +12837,19 @@
         <v>0</v>
       </c>
       <c r="AZ70" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>-0.4647231720437685</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD70" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA70" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB70" t="n">
-        <v>-0.4647231720437685</v>
-      </c>
-      <c r="BC70" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD70" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE70" t="n">
         <v>4.65</v>
@@ -13013,19 +13013,19 @@
         <v>0</v>
       </c>
       <c r="AZ71" t="n">
+        <v>0.8229838658936565</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>-0.5680647467311557</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD71" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA71" t="n">
-        <v>0.8229838658936565</v>
-      </c>
-      <c r="BB71" t="n">
-        <v>-0.5680647467311557</v>
-      </c>
-      <c r="BC71" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD71" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE71" t="n">
         <v>4.65</v>
@@ -13189,19 +13189,19 @@
         <v>1</v>
       </c>
       <c r="AZ72" t="n">
+        <v>0.7485107481711013</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD72" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>0.7485107481711013</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE72" t="n">
         <v>4.69</v>
@@ -13365,19 +13365,19 @@
         <v>0</v>
       </c>
       <c r="AZ73" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>-0.7485107481711012</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD73" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA73" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB73" t="n">
-        <v>-0.7485107481711012</v>
-      </c>
-      <c r="BC73" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE73" t="n">
         <v>4.69</v>
@@ -13541,19 +13541,19 @@
         <v>0</v>
       </c>
       <c r="AZ74" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD74" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA74" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB74" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BC74" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD74" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE74" t="n">
         <v>4.69</v>
@@ -13717,19 +13717,19 @@
         <v>0</v>
       </c>
       <c r="AZ75" t="n">
+        <v>0.4647231720437691</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD75" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA75" t="n">
-        <v>0.4647231720437691</v>
-      </c>
-      <c r="BB75" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD75" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE75" t="n">
         <v>4.69</v>
@@ -13893,19 +13893,19 @@
         <v>0</v>
       </c>
       <c r="AZ76" t="n">
+        <v>0.3546048870425358</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>-0.9350162426854147</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD76" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA76" t="n">
-        <v>0.3546048870425358</v>
-      </c>
-      <c r="BB76" t="n">
-        <v>-0.9350162426854147</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD76" t="n">
-        <v>-1</v>
       </c>
       <c r="BE76" t="n">
         <v>4.98</v>
@@ -14069,19 +14069,19 @@
         <v>0</v>
       </c>
       <c r="AZ77" t="n">
+        <v>0.2393156642875577</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>-0.970941817426052</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD77" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA77" t="n">
-        <v>0.2393156642875577</v>
-      </c>
-      <c r="BB77" t="n">
-        <v>-0.970941817426052</v>
-      </c>
-      <c r="BC77" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD77" t="n">
-        <v>-1</v>
       </c>
       <c r="BE77" t="n">
         <v>4.98</v>
@@ -14245,19 +14245,19 @@
         <v>0</v>
       </c>
       <c r="AZ78" t="n">
+        <v>0.1205366802553231</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD78" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>0.1205366802553231</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>-1</v>
       </c>
       <c r="BE78" t="n">
         <v>4.98</v>
@@ -14421,19 +14421,19 @@
         <v>0</v>
       </c>
       <c r="AZ79" t="n">
+        <v>-3.216245299353273e-16</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD79" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>-3.216245299353273e-16</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>-1</v>
       </c>
       <c r="BE79" t="n">
         <v>4.98</v>
@@ -14597,19 +14597,19 @@
         <v>0</v>
       </c>
       <c r="AZ80" t="n">
+        <v>-0.1205366802553228</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD80" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA80" t="n">
-        <v>-0.1205366802553228</v>
-      </c>
-      <c r="BB80" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BC80" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD80" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE80" t="n">
         <v>4.98</v>
@@ -14773,19 +14773,19 @@
         <v>0</v>
       </c>
       <c r="AZ81" t="n">
+        <v>-0.2393156642875574</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>-0.9709418174260521</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD81" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA81" t="n">
-        <v>-0.2393156642875574</v>
-      </c>
-      <c r="BB81" t="n">
-        <v>-0.9709418174260521</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD81" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE81" t="n">
         <v>5.57</v>
@@ -14949,19 +14949,19 @@
         <v>0</v>
       </c>
       <c r="AZ82" t="n">
+        <v>-0.3546048870425356</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>-0.9350162426854148</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD82" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>-0.3546048870425356</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>-0.9350162426854148</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE82" t="n">
         <v>5.57</v>
@@ -15125,19 +15125,19 @@
         <v>0</v>
       </c>
       <c r="AZ83" t="n">
+        <v>-0.4647231720437681</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>-0.8854560256532101</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD83" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>-0.4647231720437681</v>
-      </c>
-      <c r="BB83" t="n">
-        <v>-0.8854560256532101</v>
-      </c>
-      <c r="BC83" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD83" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE83" t="n">
         <v>5.57</v>
@@ -15301,19 +15301,19 @@
         <v>0</v>
       </c>
       <c r="AZ84" t="n">
+        <v>-0.5680647467311556</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>-0.8229838658936566</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD84" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>-0.5680647467311556</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>-0.8229838658936566</v>
-      </c>
-      <c r="BC84" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD84" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE84" t="n">
         <v>5.57</v>
@@ -15477,19 +15477,19 @@
         <v>0</v>
       </c>
       <c r="AZ85" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>-0.7485107481711013</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD85" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>-0.7485107481711013</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE85" t="n">
         <v>4.99</v>
@@ -15653,19 +15653,19 @@
         <v>0</v>
       </c>
       <c r="AZ86" t="n">
+        <v>-0.7485107481711011</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>-0.6631226582407952</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD86" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA86" t="n">
-        <v>-0.7485107481711011</v>
-      </c>
-      <c r="BB86" t="n">
-        <v>-0.6631226582407952</v>
-      </c>
-      <c r="BC86" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD86" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE86" t="n">
         <v>4.99</v>
@@ -15829,19 +15829,19 @@
         <v>0</v>
       </c>
       <c r="AZ87" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>-0.5680647467311559</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD87" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA87" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BB87" t="n">
-        <v>-0.5680647467311559</v>
-      </c>
-      <c r="BC87" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD87" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE87" t="n">
         <v>4.99</v>
@@ -16005,19 +16005,19 @@
         <v>0</v>
       </c>
       <c r="AZ88" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>-0.4647231720437691</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD88" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA88" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BB88" t="n">
-        <v>-0.4647231720437691</v>
-      </c>
-      <c r="BC88" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE88" t="n">
         <v>4.99</v>
@@ -16181,19 +16181,19 @@
         <v>0</v>
       </c>
       <c r="AZ89" t="n">
+        <v>-0.9350162426854147</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>-0.3546048870425359</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD89" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA89" t="n">
-        <v>-0.9350162426854147</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>-0.3546048870425359</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE89" t="n">
         <v>4.58</v>
@@ -16357,19 +16357,19 @@
         <v>0</v>
       </c>
       <c r="AZ90" t="n">
+        <v>-0.970941817426052</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>-0.2393156642875577</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD90" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA90" t="n">
-        <v>-0.970941817426052</v>
-      </c>
-      <c r="BB90" t="n">
-        <v>-0.2393156642875577</v>
-      </c>
-      <c r="BC90" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD90" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE90" t="n">
         <v>4.58</v>
@@ -16533,19 +16533,19 @@
         <v>0</v>
       </c>
       <c r="AZ91" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>-0.1205366802553236</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD91" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA91" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BB91" t="n">
-        <v>-0.1205366802553236</v>
-      </c>
-      <c r="BC91" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD91" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE91" t="n">
         <v>4.58</v>
@@ -16709,19 +16709,19 @@
         <v>0</v>
       </c>
       <c r="AZ92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD92" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA92" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB92" t="n">
-        <v>-1.83697019872103e-16</v>
-      </c>
-      <c r="BC92" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD92" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE92" t="n">
         <v>4.58</v>
@@ -16885,19 +16885,19 @@
         <v>0</v>
       </c>
       <c r="AZ93" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0.1205366802553232</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD93" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA93" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BB93" t="n">
-        <v>0.1205366802553232</v>
-      </c>
-      <c r="BC93" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD93" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE93" t="n">
         <v>4.58</v>
@@ -17061,19 +17061,19 @@
         <v>0</v>
       </c>
       <c r="AZ94" t="n">
+        <v>-0.9709418174260521</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0.2393156642875574</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD94" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>-0.9709418174260521</v>
-      </c>
-      <c r="BB94" t="n">
-        <v>0.2393156642875574</v>
-      </c>
-      <c r="BC94" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD94" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE94" t="n">
         <v>4.76</v>
@@ -17237,19 +17237,19 @@
         <v>0</v>
       </c>
       <c r="AZ95" t="n">
+        <v>-0.9350162426854148</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD95" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA95" t="n">
-        <v>-0.9350162426854148</v>
-      </c>
-      <c r="BB95" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC95" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD95" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE95" t="n">
         <v>4.76</v>
@@ -17413,19 +17413,19 @@
         <v>0</v>
       </c>
       <c r="AZ96" t="n">
+        <v>-0.8854560256532101</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>0.464723172043768</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD96" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA96" t="n">
-        <v>-0.8854560256532101</v>
-      </c>
-      <c r="BB96" t="n">
-        <v>0.464723172043768</v>
-      </c>
-      <c r="BC96" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD96" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE96" t="n">
         <v>4.76</v>
@@ -17589,19 +17589,19 @@
         <v>0</v>
       </c>
       <c r="AZ97" t="n">
+        <v>-0.822983865893657</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0.5680647467311548</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD97" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA97" t="n">
-        <v>-0.822983865893657</v>
-      </c>
-      <c r="BB97" t="n">
-        <v>0.5680647467311548</v>
-      </c>
-      <c r="BC97" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD97" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE97" t="n">
         <v>4.76</v>
@@ -17765,19 +17765,19 @@
         <v>0</v>
       </c>
       <c r="AZ98" t="n">
+        <v>-0.7485107481711011</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD98" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA98" t="n">
-        <v>-0.7485107481711011</v>
-      </c>
-      <c r="BB98" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BC98" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD98" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE98" t="n">
         <v>4.55</v>
@@ -17941,19 +17941,19 @@
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
+        <v>-0.6631226582407955</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0.7485107481711007</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD99" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA99" t="n">
-        <v>-0.6631226582407955</v>
-      </c>
-      <c r="BB99" t="n">
-        <v>0.7485107481711007</v>
-      </c>
-      <c r="BC99" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD99" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE99" t="n">
         <v>4.55</v>
@@ -18117,19 +18117,19 @@
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
+        <v>-0.5680647467311559</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD100" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA100" t="n">
-        <v>-0.5680647467311559</v>
-      </c>
-      <c r="BB100" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC100" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD100" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE100" t="n">
         <v>4.55</v>
@@ -18293,19 +18293,19 @@
         <v>0</v>
       </c>
       <c r="AZ101" t="n">
+        <v>-0.4647231720437684</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0.88545602565321</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD101" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA101" t="n">
-        <v>-0.4647231720437684</v>
-      </c>
-      <c r="BB101" t="n">
-        <v>0.88545602565321</v>
-      </c>
-      <c r="BC101" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD101" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE101" t="n">
         <v>4.55</v>
@@ -18469,19 +18469,19 @@
         <v>0</v>
       </c>
       <c r="AZ102" t="n">
+        <v>-0.354604887042536</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0.9350162426854147</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD102" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>-0.354604887042536</v>
-      </c>
-      <c r="BB102" t="n">
-        <v>0.9350162426854147</v>
-      </c>
-      <c r="BC102" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD102" t="n">
-        <v>1</v>
       </c>
       <c r="BE102" t="n">
         <v>4.21</v>
@@ -18645,19 +18645,19 @@
         <v>0</v>
       </c>
       <c r="AZ103" t="n">
+        <v>-0.2393156642875578</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD103" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA103" t="n">
-        <v>-0.2393156642875578</v>
-      </c>
-      <c r="BB103" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BC103" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD103" t="n">
-        <v>1</v>
       </c>
       <c r="BE103" t="n">
         <v>4.21</v>
@@ -18821,19 +18821,19 @@
         <v>0</v>
       </c>
       <c r="AZ104" t="n">
+        <v>-0.1205366802553236</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD104" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA104" t="n">
-        <v>-0.1205366802553236</v>
-      </c>
-      <c r="BB104" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BC104" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD104" t="n">
-        <v>1</v>
       </c>
       <c r="BE104" t="n">
         <v>4.21</v>
@@ -18997,19 +18997,19 @@
         <v>0</v>
       </c>
       <c r="AZ105" t="n">
+        <v>6.432490598706546e-16</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD105" t="n">
         <v>88.40000000000001</v>
-      </c>
-      <c r="BA105" t="n">
-        <v>6.432490598706546e-16</v>
-      </c>
-      <c r="BB105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC105" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD105" t="n">
-        <v>1</v>
       </c>
       <c r="BE105" t="n">
         <v>4.21</v>
@@ -19173,19 +19173,19 @@
         <v>0</v>
       </c>
       <c r="AZ106" t="n">
-        <v>85.25714285714285</v>
+        <v>0.120536680255323</v>
       </c>
       <c r="BA106" t="n">
-        <v>0.120536680255323</v>
+        <v>0.992708874098054</v>
       </c>
       <c r="BB106" t="n">
-        <v>0.992708874098054</v>
+        <v>-2.449293598294706e-16</v>
       </c>
       <c r="BC106" t="n">
-        <v>-2.449293598294706e-16</v>
+        <v>1</v>
       </c>
       <c r="BD106" t="n">
-        <v>1</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="BE106" t="n">
         <v>4.21</v>
@@ -19349,19 +19349,19 @@
         <v>0</v>
       </c>
       <c r="AZ107" t="n">
-        <v>84</v>
+        <v>0.2393156642875577</v>
       </c>
       <c r="BA107" t="n">
-        <v>0.2393156642875577</v>
+        <v>0.970941817426052</v>
       </c>
       <c r="BB107" t="n">
-        <v>0.970941817426052</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="BC107" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="BD107" t="n">
-        <v>0.8660254037844387</v>
+        <v>85.25714285714285</v>
       </c>
       <c r="BE107" t="n">
         <v>3.59</v>
@@ -19525,19 +19525,19 @@
         <v>0</v>
       </c>
       <c r="AZ108" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD108" t="n">
         <v>84</v>
-      </c>
-      <c r="BA108" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BB108" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BC108" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD108" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE108" t="n">
         <v>3.59</v>
@@ -19701,19 +19701,19 @@
         <v>0</v>
       </c>
       <c r="AZ109" t="n">
+        <v>0.4647231720437685</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD109" t="n">
         <v>84</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>0.4647231720437685</v>
-      </c>
-      <c r="BB109" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BC109" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD109" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE109" t="n">
         <v>3.59</v>
@@ -19877,19 +19877,19 @@
         <v>0</v>
       </c>
       <c r="AZ110" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD110" t="n">
         <v>84</v>
-      </c>
-      <c r="BA110" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB110" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC110" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD110" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE110" t="n">
         <v>3.59</v>
@@ -20053,19 +20053,19 @@
         <v>0</v>
       </c>
       <c r="AZ111" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD111" t="n">
         <v>84</v>
-      </c>
-      <c r="BA111" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB111" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BC111" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD111" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE111" t="n">
         <v>3.77</v>
@@ -20229,19 +20229,19 @@
         <v>0</v>
       </c>
       <c r="AZ112" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0.6631226582407953</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD112" t="n">
         <v>84</v>
-      </c>
-      <c r="BA112" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BB112" t="n">
-        <v>0.6631226582407953</v>
-      </c>
-      <c r="BC112" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD112" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE112" t="n">
         <v>3.77</v>
@@ -20405,19 +20405,19 @@
         <v>0</v>
       </c>
       <c r="AZ113" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>0.5680647467311559</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD113" t="n">
         <v>84</v>
-      </c>
-      <c r="BA113" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BB113" t="n">
-        <v>0.5680647467311559</v>
-      </c>
-      <c r="BC113" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD113" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE113" t="n">
         <v>3.77</v>
@@ -20581,19 +20581,19 @@
         <v>0</v>
       </c>
       <c r="AZ114" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>0.4647231720437686</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD114" t="n">
         <v>84</v>
-      </c>
-      <c r="BA114" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB114" t="n">
-        <v>0.4647231720437686</v>
-      </c>
-      <c r="BC114" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD114" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE114" t="n">
         <v>3.77</v>
@@ -20757,19 +20757,19 @@
         <v>0</v>
       </c>
       <c r="AZ115" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD115" t="n">
         <v>84</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB115" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD115" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE115" t="n">
         <v>3.8</v>
@@ -20933,19 +20933,19 @@
         <v>0</v>
       </c>
       <c r="AZ116" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0.239315664287558</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD116" t="n">
         <v>84</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BB116" t="n">
-        <v>0.239315664287558</v>
-      </c>
-      <c r="BC116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE116" t="n">
         <v>3.8</v>
@@ -21109,19 +21109,19 @@
         <v>0</v>
       </c>
       <c r="AZ117" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.120536680255323</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD117" t="n">
         <v>84</v>
-      </c>
-      <c r="BA117" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB117" t="n">
-        <v>0.120536680255323</v>
-      </c>
-      <c r="BC117" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD117" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE117" t="n">
         <v>3.8</v>
@@ -21285,19 +21285,19 @@
         <v>0</v>
       </c>
       <c r="AZ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>-1.608122649676637e-16</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD118" t="n">
         <v>84</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>-1.608122649676637e-16</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE118" t="n">
         <v>3.8</v>
@@ -21461,19 +21461,19 @@
         <v>0</v>
       </c>
       <c r="AZ119" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.1205366802553229</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD119" t="n">
         <v>84</v>
-      </c>
-      <c r="BA119" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB119" t="n">
-        <v>-0.1205366802553229</v>
-      </c>
-      <c r="BC119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD119" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE119" t="n">
         <v>3.8</v>
@@ -21637,19 +21637,19 @@
         <v>0</v>
       </c>
       <c r="AZ120" t="n">
+        <v>0.9709418174260521</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.2393156642875575</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD120" t="n">
         <v>84</v>
-      </c>
-      <c r="BA120" t="n">
-        <v>0.9709418174260521</v>
-      </c>
-      <c r="BB120" t="n">
-        <v>-0.2393156642875575</v>
-      </c>
-      <c r="BC120" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD120" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE120" t="n">
         <v>3.93</v>
@@ -21813,19 +21813,19 @@
         <v>0</v>
       </c>
       <c r="AZ121" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.3546048870425355</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD121" t="n">
         <v>84</v>
-      </c>
-      <c r="BA121" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB121" t="n">
-        <v>-0.3546048870425355</v>
-      </c>
-      <c r="BC121" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD121" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE121" t="n">
         <v>3.93</v>
@@ -21989,19 +21989,19 @@
         <v>0</v>
       </c>
       <c r="AZ122" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.4647231720437685</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD122" t="n">
         <v>84</v>
-      </c>
-      <c r="BA122" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB122" t="n">
-        <v>-0.4647231720437685</v>
-      </c>
-      <c r="BC122" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD122" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE122" t="n">
         <v>3.93</v>
@@ -22165,19 +22165,19 @@
         <v>0</v>
       </c>
       <c r="AZ123" t="n">
+        <v>0.8229838658936565</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>-0.5680647467311557</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD123" t="n">
         <v>84</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>0.8229838658936565</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>-0.5680647467311557</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE123" t="n">
         <v>3.93</v>
@@ -22341,19 +22341,19 @@
         <v>1</v>
       </c>
       <c r="AZ124" t="n">
+        <v>0.7485107481711013</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD124" t="n">
         <v>84</v>
-      </c>
-      <c r="BA124" t="n">
-        <v>0.7485107481711013</v>
-      </c>
-      <c r="BB124" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BC124" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD124" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE124" t="n">
         <v>4.42</v>
@@ -22517,19 +22517,19 @@
         <v>0</v>
       </c>
       <c r="AZ125" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.7485107481711012</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD125" t="n">
         <v>84</v>
-      </c>
-      <c r="BA125" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB125" t="n">
-        <v>-0.7485107481711012</v>
-      </c>
-      <c r="BC125" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD125" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE125" t="n">
         <v>4.42</v>
@@ -22693,19 +22693,19 @@
         <v>0</v>
       </c>
       <c r="AZ126" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD126" t="n">
         <v>84</v>
-      </c>
-      <c r="BA126" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB126" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BC126" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD126" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE126" t="n">
         <v>4.42</v>
@@ -22869,19 +22869,19 @@
         <v>0</v>
       </c>
       <c r="AZ127" t="n">
+        <v>0.4647231720437691</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD127" t="n">
         <v>84</v>
-      </c>
-      <c r="BA127" t="n">
-        <v>0.4647231720437691</v>
-      </c>
-      <c r="BB127" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BC127" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD127" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE127" t="n">
         <v>4.42</v>
@@ -23045,19 +23045,19 @@
         <v>0</v>
       </c>
       <c r="AZ128" t="n">
+        <v>0.3546048870425358</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>-0.9350162426854147</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD128" t="n">
         <v>84</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>0.3546048870425358</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>-0.9350162426854147</v>
-      </c>
-      <c r="BC128" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD128" t="n">
-        <v>-1</v>
       </c>
       <c r="BE128" t="n">
         <v>4.32</v>
@@ -23221,19 +23221,19 @@
         <v>0</v>
       </c>
       <c r="AZ129" t="n">
+        <v>0.2393156642875577</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>-0.970941817426052</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD129" t="n">
         <v>84</v>
-      </c>
-      <c r="BA129" t="n">
-        <v>0.2393156642875577</v>
-      </c>
-      <c r="BB129" t="n">
-        <v>-0.970941817426052</v>
-      </c>
-      <c r="BC129" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD129" t="n">
-        <v>-1</v>
       </c>
       <c r="BE129" t="n">
         <v>4.32</v>
@@ -23397,19 +23397,19 @@
         <v>0</v>
       </c>
       <c r="AZ130" t="n">
+        <v>0.1205366802553231</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD130" t="n">
         <v>84</v>
-      </c>
-      <c r="BA130" t="n">
-        <v>0.1205366802553231</v>
-      </c>
-      <c r="BB130" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BC130" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD130" t="n">
-        <v>-1</v>
       </c>
       <c r="BE130" t="n">
         <v>4.32</v>
@@ -23573,19 +23573,19 @@
         <v>0</v>
       </c>
       <c r="AZ131" t="n">
+        <v>-3.216245299353273e-16</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD131" t="n">
         <v>84</v>
-      </c>
-      <c r="BA131" t="n">
-        <v>-3.216245299353273e-16</v>
-      </c>
-      <c r="BB131" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC131" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD131" t="n">
-        <v>-1</v>
       </c>
       <c r="BE131" t="n">
         <v>4.32</v>
@@ -23749,19 +23749,19 @@
         <v>0</v>
       </c>
       <c r="AZ132" t="n">
+        <v>-0.1205366802553228</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD132" t="n">
         <v>84</v>
-      </c>
-      <c r="BA132" t="n">
-        <v>-0.1205366802553228</v>
-      </c>
-      <c r="BB132" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BC132" t="n">
-        <v>1.224646799147353e-16</v>
-      </c>
-      <c r="BD132" t="n">
-        <v>-1</v>
       </c>
       <c r="BE132" t="n">
         <v>4.32</v>
@@ -23925,19 +23925,19 @@
         <v>0</v>
       </c>
       <c r="AZ133" t="n">
+        <v>-0.2393156642875574</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.9709418174260521</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD133" t="n">
         <v>84</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>-0.2393156642875574</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>-0.9709418174260521</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE133" t="n">
         <v>3.51</v>
@@ -24101,19 +24101,19 @@
         <v>0</v>
       </c>
       <c r="AZ134" t="n">
+        <v>-0.3546048870425356</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.9350162426854148</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD134" t="n">
         <v>84</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>-0.3546048870425356</v>
-      </c>
-      <c r="BB134" t="n">
-        <v>-0.9350162426854148</v>
-      </c>
-      <c r="BC134" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE134" t="n">
         <v>3.51</v>
@@ -24277,19 +24277,19 @@
         <v>0</v>
       </c>
       <c r="AZ135" t="n">
+        <v>-0.4647231720437681</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.8854560256532101</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD135" t="n">
         <v>84</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>-0.4647231720437681</v>
-      </c>
-      <c r="BB135" t="n">
-        <v>-0.8854560256532101</v>
-      </c>
-      <c r="BC135" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD135" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE135" t="n">
         <v>3.51</v>
@@ -24453,19 +24453,19 @@
         <v>0</v>
       </c>
       <c r="AZ136" t="n">
+        <v>-0.5680647467311556</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.8229838658936566</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="BD136" t="n">
         <v>84</v>
-      </c>
-      <c r="BA136" t="n">
-        <v>-0.5680647467311556</v>
-      </c>
-      <c r="BB136" t="n">
-        <v>-0.8229838658936566</v>
-      </c>
-      <c r="BC136" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="BD136" t="n">
-        <v>-0.8660254037844388</v>
       </c>
       <c r="BE136" t="n">
         <v>3.51</v>
@@ -24629,19 +24629,19 @@
         <v>0</v>
       </c>
       <c r="AZ137" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.7485107481711013</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD137" t="n">
         <v>84</v>
-      </c>
-      <c r="BA137" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BB137" t="n">
-        <v>-0.7485107481711013</v>
-      </c>
-      <c r="BC137" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD137" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE137" t="n">
         <v>3.57</v>
@@ -24805,19 +24805,19 @@
         <v>0</v>
       </c>
       <c r="AZ138" t="n">
+        <v>-0.7485107481711011</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>-0.6631226582407952</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD138" t="n">
         <v>84</v>
-      </c>
-      <c r="BA138" t="n">
-        <v>-0.7485107481711011</v>
-      </c>
-      <c r="BB138" t="n">
-        <v>-0.6631226582407952</v>
-      </c>
-      <c r="BC138" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD138" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE138" t="n">
         <v>3.57</v>
@@ -24981,19 +24981,19 @@
         <v>0</v>
       </c>
       <c r="AZ139" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>-0.5680647467311559</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD139" t="n">
         <v>84</v>
-      </c>
-      <c r="BA139" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BB139" t="n">
-        <v>-0.5680647467311559</v>
-      </c>
-      <c r="BC139" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD139" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE139" t="n">
         <v>3.57</v>
@@ -25157,19 +25157,19 @@
         <v>0</v>
       </c>
       <c r="AZ140" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>-0.4647231720437691</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BD140" t="n">
         <v>84</v>
-      </c>
-      <c r="BA140" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BB140" t="n">
-        <v>-0.4647231720437691</v>
-      </c>
-      <c r="BC140" t="n">
-        <v>-0.8660254037844385</v>
-      </c>
-      <c r="BD140" t="n">
-        <v>-0.5000000000000004</v>
       </c>
       <c r="BE140" t="n">
         <v>3.57</v>
@@ -25333,19 +25333,19 @@
         <v>0</v>
       </c>
       <c r="AZ141" t="n">
+        <v>-0.9350162426854147</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>-0.3546048870425359</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD141" t="n">
         <v>84</v>
-      </c>
-      <c r="BA141" t="n">
-        <v>-0.9350162426854147</v>
-      </c>
-      <c r="BB141" t="n">
-        <v>-0.3546048870425359</v>
-      </c>
-      <c r="BC141" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD141" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE141" t="n">
         <v>3.57</v>
@@ -25509,19 +25509,19 @@
         <v>0</v>
       </c>
       <c r="AZ142" t="n">
+        <v>-0.970941817426052</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.2393156642875577</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD142" t="n">
         <v>84</v>
-      </c>
-      <c r="BA142" t="n">
-        <v>-0.970941817426052</v>
-      </c>
-      <c r="BB142" t="n">
-        <v>-0.2393156642875577</v>
-      </c>
-      <c r="BC142" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD142" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE142" t="n">
         <v>3.76</v>
@@ -25685,19 +25685,19 @@
         <v>0</v>
       </c>
       <c r="AZ143" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.1205366802553236</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD143" t="n">
         <v>84</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BB143" t="n">
-        <v>-0.1205366802553236</v>
-      </c>
-      <c r="BC143" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE143" t="n">
         <v>3.76</v>
@@ -25861,19 +25861,19 @@
         <v>0</v>
       </c>
       <c r="AZ144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD144" t="n">
         <v>84</v>
-      </c>
-      <c r="BA144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB144" t="n">
-        <v>-1.83697019872103e-16</v>
-      </c>
-      <c r="BC144" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD144" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE144" t="n">
         <v>3.76</v>
@@ -26037,19 +26037,19 @@
         <v>0</v>
       </c>
       <c r="AZ145" t="n">
+        <v>-0.992708874098054</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>0.1205366802553232</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="BD145" t="n">
         <v>84</v>
-      </c>
-      <c r="BA145" t="n">
-        <v>-0.992708874098054</v>
-      </c>
-      <c r="BB145" t="n">
-        <v>0.1205366802553232</v>
-      </c>
-      <c r="BC145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD145" t="n">
-        <v>-1.83697019872103e-16</v>
       </c>
       <c r="BE145" t="n">
         <v>3.76</v>
@@ -26213,19 +26213,19 @@
         <v>0</v>
       </c>
       <c r="AZ146" t="n">
+        <v>-0.9709418174260521</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>0.2393156642875574</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD146" t="n">
         <v>84</v>
-      </c>
-      <c r="BA146" t="n">
-        <v>-0.9709418174260521</v>
-      </c>
-      <c r="BB146" t="n">
-        <v>0.2393156642875574</v>
-      </c>
-      <c r="BC146" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD146" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE146" t="n">
         <v>3.57</v>
@@ -26389,19 +26389,19 @@
         <v>0</v>
       </c>
       <c r="AZ147" t="n">
+        <v>-0.9350162426854148</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD147" t="n">
         <v>84</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>-0.9350162426854148</v>
-      </c>
-      <c r="BB147" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC147" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD147" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE147" t="n">
         <v>3.57</v>
@@ -26565,19 +26565,19 @@
         <v>0</v>
       </c>
       <c r="AZ148" t="n">
+        <v>-0.8854560256532101</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>0.464723172043768</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD148" t="n">
         <v>84</v>
-      </c>
-      <c r="BA148" t="n">
-        <v>-0.8854560256532101</v>
-      </c>
-      <c r="BB148" t="n">
-        <v>0.464723172043768</v>
-      </c>
-      <c r="BC148" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD148" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE148" t="n">
         <v>3.57</v>
@@ -26741,19 +26741,19 @@
         <v>0</v>
       </c>
       <c r="AZ149" t="n">
+        <v>-0.822983865893657</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>0.5680647467311548</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD149" t="n">
         <v>84</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>-0.822983865893657</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>0.5680647467311548</v>
-      </c>
-      <c r="BC149" t="n">
-        <v>-0.8660254037844386</v>
-      </c>
-      <c r="BD149" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE149" t="n">
         <v>3.57</v>
@@ -26917,19 +26917,19 @@
         <v>0</v>
       </c>
       <c r="AZ150" t="n">
+        <v>-0.7485107481711011</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD150" t="n">
         <v>84</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>-0.7485107481711011</v>
-      </c>
-      <c r="BB150" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BC150" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD150" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE150" t="n">
         <v>3.8</v>
@@ -27093,19 +27093,19 @@
         <v>0</v>
       </c>
       <c r="AZ151" t="n">
+        <v>-0.6631226582407955</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>0.7485107481711007</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD151" t="n">
         <v>84</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>-0.6631226582407955</v>
-      </c>
-      <c r="BB151" t="n">
-        <v>0.7485107481711007</v>
-      </c>
-      <c r="BC151" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD151" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE151" t="n">
         <v>3.8</v>
@@ -27269,19 +27269,19 @@
         <v>0</v>
       </c>
       <c r="AZ152" t="n">
+        <v>-0.5680647467311559</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD152" t="n">
         <v>84</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>-0.5680647467311559</v>
-      </c>
-      <c r="BB152" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC152" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD152" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE152" t="n">
         <v>3.8</v>
@@ -27445,19 +27445,19 @@
         <v>0</v>
       </c>
       <c r="AZ153" t="n">
+        <v>-0.4647231720437684</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>0.88545602565321</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="BD153" t="n">
         <v>84</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>-0.4647231720437684</v>
-      </c>
-      <c r="BB153" t="n">
-        <v>0.88545602565321</v>
-      </c>
-      <c r="BC153" t="n">
-        <v>-0.5000000000000004</v>
-      </c>
-      <c r="BD153" t="n">
-        <v>0.8660254037844384</v>
       </c>
       <c r="BE153" t="n">
         <v>3.8</v>
@@ -27621,19 +27621,19 @@
         <v>0</v>
       </c>
       <c r="AZ154" t="n">
+        <v>-0.354604887042536</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>0.9350162426854147</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD154" t="n">
         <v>84</v>
-      </c>
-      <c r="BA154" t="n">
-        <v>-0.354604887042536</v>
-      </c>
-      <c r="BB154" t="n">
-        <v>0.9350162426854147</v>
-      </c>
-      <c r="BC154" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD154" t="n">
-        <v>1</v>
       </c>
       <c r="BE154" t="n">
         <v>3.8</v>
@@ -27797,19 +27797,19 @@
         <v>0</v>
       </c>
       <c r="AZ155" t="n">
+        <v>-0.2393156642875578</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD155" t="n">
         <v>84</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>-0.2393156642875578</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>1</v>
       </c>
       <c r="BE155" t="n">
         <v>3.69</v>
@@ -27973,19 +27973,19 @@
         <v>0</v>
       </c>
       <c r="AZ156" t="n">
+        <v>-0.1205366802553236</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD156" t="n">
         <v>84</v>
-      </c>
-      <c r="BA156" t="n">
-        <v>-0.1205366802553236</v>
-      </c>
-      <c r="BB156" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BC156" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD156" t="n">
-        <v>1</v>
       </c>
       <c r="BE156" t="n">
         <v>3.69</v>
@@ -28149,19 +28149,19 @@
         <v>0</v>
       </c>
       <c r="AZ157" t="n">
+        <v>6.432490598706546e-16</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD157" t="n">
         <v>84</v>
-      </c>
-      <c r="BA157" t="n">
-        <v>6.432490598706546e-16</v>
-      </c>
-      <c r="BB157" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC157" t="n">
-        <v>-2.449293598294706e-16</v>
-      </c>
-      <c r="BD157" t="n">
-        <v>1</v>
       </c>
       <c r="BE157" t="n">
         <v>3.69</v>
@@ -28325,19 +28325,19 @@
         <v>0</v>
       </c>
       <c r="AZ158" t="n">
-        <v>82.85714285714286</v>
+        <v>0.120536680255323</v>
       </c>
       <c r="BA158" t="n">
-        <v>0.120536680255323</v>
+        <v>0.992708874098054</v>
       </c>
       <c r="BB158" t="n">
-        <v>0.992708874098054</v>
+        <v>-2.449293598294706e-16</v>
       </c>
       <c r="BC158" t="n">
-        <v>-2.449293598294706e-16</v>
+        <v>1</v>
       </c>
       <c r="BD158" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="BE158" t="n">
         <v>3.69</v>
@@ -28501,19 +28501,19 @@
         <v>0</v>
       </c>
       <c r="AZ159" t="n">
-        <v>82</v>
+        <v>0.2393156642875577</v>
       </c>
       <c r="BA159" t="n">
-        <v>0.2393156642875577</v>
+        <v>0.970941817426052</v>
       </c>
       <c r="BB159" t="n">
-        <v>0.970941817426052</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="BC159" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.8660254037844387</v>
       </c>
       <c r="BD159" t="n">
-        <v>0.8660254037844387</v>
+        <v>82.85714285714286</v>
       </c>
       <c r="BE159" t="n">
         <v>3.79</v>
@@ -28677,19 +28677,19 @@
         <v>0</v>
       </c>
       <c r="AZ160" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD160" t="n">
         <v>82</v>
-      </c>
-      <c r="BA160" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BB160" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BC160" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD160" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE160" t="n">
         <v>3.79</v>
@@ -28853,19 +28853,19 @@
         <v>0</v>
       </c>
       <c r="AZ161" t="n">
+        <v>0.4647231720437685</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD161" t="n">
         <v>82</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>0.4647231720437685</v>
-      </c>
-      <c r="BB161" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BC161" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE161" t="n">
         <v>3.79</v>
@@ -29029,19 +29029,19 @@
         <v>0</v>
       </c>
       <c r="AZ162" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BD162" t="n">
         <v>82</v>
-      </c>
-      <c r="BA162" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB162" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BC162" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD162" t="n">
-        <v>0.8660254037844387</v>
       </c>
       <c r="BE162" t="n">
         <v>3.79</v>
@@ -29205,19 +29205,19 @@
         <v>0</v>
       </c>
       <c r="AZ163" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD163" t="n">
         <v>82</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB163" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BC163" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD163" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE163" t="n">
         <v>4.02</v>
@@ -29381,19 +29381,19 @@
         <v>0</v>
       </c>
       <c r="AZ164" t="n">
+        <v>0.7485107481711011</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>0.6631226582407953</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD164" t="n">
         <v>82</v>
-      </c>
-      <c r="BA164" t="n">
-        <v>0.7485107481711011</v>
-      </c>
-      <c r="BB164" t="n">
-        <v>0.6631226582407953</v>
-      </c>
-      <c r="BC164" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD164" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE164" t="n">
         <v>4.02</v>
@@ -29557,19 +29557,19 @@
         <v>0</v>
       </c>
       <c r="AZ165" t="n">
+        <v>0.8229838658936564</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>0.5680647467311559</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD165" t="n">
         <v>82</v>
-      </c>
-      <c r="BA165" t="n">
-        <v>0.8229838658936564</v>
-      </c>
-      <c r="BB165" t="n">
-        <v>0.5680647467311559</v>
-      </c>
-      <c r="BC165" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD165" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE165" t="n">
         <v>4.02</v>
@@ -29733,19 +29733,19 @@
         <v>0</v>
       </c>
       <c r="AZ166" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0.4647231720437686</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="BD166" t="n">
         <v>82</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB166" t="n">
-        <v>0.4647231720437686</v>
-      </c>
-      <c r="BC166" t="n">
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="BD166" t="n">
-        <v>0.5000000000000001</v>
       </c>
       <c r="BE166" t="n">
         <v>4.02</v>
@@ -29909,19 +29909,19 @@
         <v>0</v>
       </c>
       <c r="AZ167" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>0.3546048870425356</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD167" t="n">
         <v>82</v>
-      </c>
-      <c r="BA167" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB167" t="n">
-        <v>0.3546048870425356</v>
-      </c>
-      <c r="BC167" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD167" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE167" t="n">
         <v>4.59</v>
@@ -30085,19 +30085,19 @@
         <v>0</v>
       </c>
       <c r="AZ168" t="n">
+        <v>0.970941817426052</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>0.239315664287558</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD168" t="n">
         <v>82</v>
-      </c>
-      <c r="BA168" t="n">
-        <v>0.970941817426052</v>
-      </c>
-      <c r="BB168" t="n">
-        <v>0.239315664287558</v>
-      </c>
-      <c r="BC168" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD168" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE168" t="n">
         <v>4.59</v>
@@ -30261,19 +30261,19 @@
         <v>0</v>
       </c>
       <c r="AZ169" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>0.120536680255323</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD169" t="n">
         <v>82</v>
-      </c>
-      <c r="BA169" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB169" t="n">
-        <v>0.120536680255323</v>
-      </c>
-      <c r="BC169" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD169" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE169" t="n">
         <v>4.59</v>
@@ -30437,19 +30437,19 @@
         <v>0</v>
       </c>
       <c r="AZ170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>-1.608122649676637e-16</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD170" t="n">
         <v>82</v>
-      </c>
-      <c r="BA170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB170" t="n">
-        <v>-1.608122649676637e-16</v>
-      </c>
-      <c r="BC170" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD170" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE170" t="n">
         <v>4.59</v>
@@ -30613,19 +30613,19 @@
         <v>0</v>
       </c>
       <c r="AZ171" t="n">
+        <v>0.992708874098054</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>-0.1205366802553229</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="BD171" t="n">
         <v>82</v>
-      </c>
-      <c r="BA171" t="n">
-        <v>0.992708874098054</v>
-      </c>
-      <c r="BB171" t="n">
-        <v>-0.1205366802553229</v>
-      </c>
-      <c r="BC171" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD171" t="n">
-        <v>6.123233995736766e-17</v>
       </c>
       <c r="BE171" t="n">
         <v>4.59</v>
@@ -30789,19 +30789,19 @@
         <v>0</v>
       </c>
       <c r="AZ172" t="n">
+        <v>0.9709418174260521</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>-0.2393156642875575</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD172" t="n">
         <v>82</v>
-      </c>
-      <c r="BA172" t="n">
-        <v>0.9709418174260521</v>
-      </c>
-      <c r="BB172" t="n">
-        <v>-0.2393156642875575</v>
-      </c>
-      <c r="BC172" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD172" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE172" t="n">
         <v>4.45</v>
@@ -30965,19 +30965,19 @@
         <v>0</v>
       </c>
       <c r="AZ173" t="n">
+        <v>0.9350162426854148</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>-0.3546048870425355</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD173" t="n">
         <v>82</v>
-      </c>
-      <c r="BA173" t="n">
-        <v>0.9350162426854148</v>
-      </c>
-      <c r="BB173" t="n">
-        <v>-0.3546048870425355</v>
-      </c>
-      <c r="BC173" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD173" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE173" t="n">
         <v>4.45</v>
@@ -31141,19 +31141,19 @@
         <v>0</v>
       </c>
       <c r="AZ174" t="n">
+        <v>0.8854560256532099</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>-0.4647231720437685</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD174" t="n">
         <v>82</v>
-      </c>
-      <c r="BA174" t="n">
-        <v>0.8854560256532099</v>
-      </c>
-      <c r="BB174" t="n">
-        <v>-0.4647231720437685</v>
-      </c>
-      <c r="BC174" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD174" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE174" t="n">
         <v>4.45</v>
@@ -31317,19 +31317,19 @@
         <v>0</v>
       </c>
       <c r="AZ175" t="n">
+        <v>0.8229838658936565</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>-0.5680647467311557</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="BD175" t="n">
         <v>82</v>
-      </c>
-      <c r="BA175" t="n">
-        <v>0.8229838658936565</v>
-      </c>
-      <c r="BB175" t="n">
-        <v>-0.5680647467311557</v>
-      </c>
-      <c r="BC175" t="n">
-        <v>0.8660254037844387</v>
-      </c>
-      <c r="BD175" t="n">
-        <v>-0.4999999999999998</v>
       </c>
       <c r="BE175" t="n">
         <v>4.45</v>
@@ -31493,19 +31493,19 @@
         <v>1</v>
       </c>
       <c r="AZ176" t="n">
+        <v>0.7485107481711013</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>-0.663122658240795</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD176" t="n">
         <v>82</v>
-      </c>
-      <c r="BA176" t="n">
-        <v>0.7485107481711013</v>
-      </c>
-      <c r="BB176" t="n">
-        <v>-0.663122658240795</v>
-      </c>
-      <c r="BC176" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD176" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE176" t="n">
         <v>3.94</v>
@@ -31669,19 +31669,19 @@
         <v>0</v>
       </c>
       <c r="AZ177" t="n">
+        <v>0.6631226582407952</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>-0.7485107481711012</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD177" t="n">
         <v>82</v>
-      </c>
-      <c r="BA177" t="n">
-        <v>0.6631226582407952</v>
-      </c>
-      <c r="BB177" t="n">
-        <v>-0.7485107481711012</v>
-      </c>
-      <c r="BC177" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD177" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE177" t="n">
         <v>3.94</v>
@@ -31845,19 +31845,19 @@
         <v>0</v>
       </c>
       <c r="AZ178" t="n">
+        <v>0.5680647467311558</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>-0.8229838658936564</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD178" t="n">
         <v>82</v>
-      </c>
-      <c r="BA178" t="n">
-        <v>0.5680647467311558</v>
-      </c>
-      <c r="BB178" t="n">
-        <v>-0.8229838658936564</v>
-      </c>
-      <c r="BC178" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD178" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE178" t="n">
         <v>3.94</v>
@@ -32021,19 +32021,19 @@
         <v>0</v>
       </c>
       <c r="AZ179" t="n">
+        <v>0.4647231720437691</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>-0.8854560256532096</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="BD179" t="n">
         <v>82</v>
-      </c>
-      <c r="BA179" t="n">
-        <v>0.4647231720437691</v>
-      </c>
-      <c r="BB179" t="n">
-        <v>-0.8854560256532096</v>
-      </c>
-      <c r="BC179" t="n">
-        <v>0.4999999999999999</v>
-      </c>
-      <c r="BD179" t="n">
-        <v>-0.8660254037844387</v>
       </c>
       <c r="BE179" t="n">
         <v>3.94</v>
@@ -32053,7 +32053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32072,6 +32072,16 @@
           <t>disponibilidad</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rezago_semanas</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32089,6 +32099,14 @@
           <t>inicio de semana</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32106,6 +32124,14 @@
           <t>observado después de cerrar la semana</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32123,6 +32149,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32140,6 +32174,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32157,6 +32199,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32174,6 +32224,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32191,6 +32249,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32208,6 +32274,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32225,6 +32299,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32242,6 +32324,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32259,6 +32349,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32276,6 +32374,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32293,6 +32399,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32310,6 +32424,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32327,6 +32449,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32344,6 +32474,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32361,6 +32499,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32378,6 +32524,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32395,6 +32549,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -32412,6 +32574,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -32429,6 +32599,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -32446,6 +32624,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -32463,6 +32649,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -32480,6 +32674,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -32497,6 +32699,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -32514,6 +32724,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -32531,6 +32749,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -32548,6 +32774,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -32565,6 +32799,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -32582,6 +32824,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -32599,6 +32849,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -32616,6 +32874,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -32633,6 +32899,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -32650,6 +32924,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -32667,6 +32949,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -32684,6 +32974,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -32701,6 +32999,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -32718,6 +33024,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -32735,6 +33049,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -32752,6 +33074,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -32769,6 +33099,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -32786,6 +33124,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -32803,6 +33149,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -32820,6 +33174,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -32837,6 +33199,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -32854,6 +33224,14 @@
           <t>antes del pronóstico</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -32871,6 +33249,14 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>calendario de festividades</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -32888,6 +33274,14 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>calendario de pagos</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -32905,6 +33299,14 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>calendario comercial</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -32922,6 +33324,14 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>calendario comercial</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -32939,11 +33349,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>calendario comercial</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>exog_nacimientos_indice_semanal</t>
+          <t>exog_semana_anio_sin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -32956,11 +33374,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>exog_semana_anio_sin</t>
+          <t>exog_semana_anio_cos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -32973,11 +33399,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>exog_semana_anio_cos</t>
+          <t>exog_mes_sin</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -32990,11 +33424,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>exog_mes_sin</t>
+          <t>exog_mes_cos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -33007,11 +33449,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>derivada del calendario o registro de disponibilidad</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>exog_mes_cos</t>
+          <t>exog_nacimientos_indice_publicado_lag_1s</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -33024,11 +33474,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>índice demográfico histórico</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>exog_inpc_publicado</t>
+          <t>exog_inpc_publicado_lag_1s</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -33041,11 +33499,19 @@
           <t>conocida o publicada antes del pronóstico</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>INPC publicado</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>exog_temperatura_lag_1s</t>
+          <t>exog_temperatura_publicado_lag_1s</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -33057,6 +33523,14 @@
         <is>
           <t>conocida o publicada antes del pronóstico</t>
         </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>temperatura histórica regional</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
